--- a/mapeo_maestro.xlsx
+++ b/mapeo_maestro.xlsx
@@ -5,26 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilson.rojas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sleppetorcagobcl-my.sharepoint.com/personal/wilson_rojas_sleppetorca_gob_cl/Documents/Proyecto Centralizacion Remuneraciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D15125C-1E58-4F53-9F71-3E8ADE4D4DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_EA5C713F984F649B7B9FB954BD1AAC43572D4901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B76E983-31CF-49E8-B5F1-587EF3C1B6DB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2475" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-3585" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CompletarAqui" sheetId="1" r:id="rId1"/>
     <sheet name="ComoUsarlo" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompletarAqui!$A$1:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompletarAqui!$A$1:$J$185</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="247">
   <si>
     <t>estado</t>
   </si>
@@ -104,6 +104,12 @@
     <t>COMPLETAR</t>
   </si>
   <si>
+    <t>10012</t>
+  </si>
+  <si>
+    <t>BONO ALTA CONCENTRACION NO DOCENTE</t>
+  </si>
+  <si>
     <t>10014</t>
   </si>
   <si>
@@ -131,6 +137,12 @@
     <t>PLANILLA COMPLEMENTARIA (ART 42 T)</t>
   </si>
   <si>
+    <t>10050</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIG ALUM PRIORITARIOS</t>
+  </si>
+  <si>
     <t>10053</t>
   </si>
   <si>
@@ -179,6 +191,12 @@
     <t>DIFERENCIA DE SUELDO</t>
   </si>
   <si>
+    <t>10080</t>
+  </si>
+  <si>
+    <t>DIFERENCIA BIENIOS</t>
+  </si>
+  <si>
     <t>10082</t>
   </si>
   <si>
@@ -191,6 +209,12 @@
     <t>ASIG ENCARGADO DE CONVIVENCIA ESCOLAR</t>
   </si>
   <si>
+    <t>10086</t>
+  </si>
+  <si>
+    <t>SNED ASISTENTES</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
@@ -242,15 +266,63 @@
     <t>COTIZACIÓN EXPECTATIVAS DE VIDA</t>
   </si>
   <si>
+    <t>CODIGO DEL TRABAJO</t>
+  </si>
+  <si>
+    <t>ASIGNACION DE HOMOLOGACION LEY 20905</t>
+  </si>
+  <si>
+    <t>ASIGNACION CARRERA DOCENTE PARVULARIA</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>INCREMENTO 5%</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>10006</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
+    <t>ASIGNACION DE RESPONSABILIDAD</t>
+  </si>
+  <si>
+    <t>10017</t>
+  </si>
+  <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>BONO DE INCENTIVO</t>
+  </si>
+  <si>
+    <t>10022</t>
+  </si>
+  <si>
+    <t>RETROACTIVO SUELDO BASE</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>32029</t>
+  </si>
+  <si>
+    <t>32030</t>
+  </si>
+  <si>
     <t>CONTRATA</t>
   </si>
   <si>
     <t>10007</t>
   </si>
   <si>
-    <t>ASIGNACION DE RESPONSABILIDAD</t>
-  </si>
-  <si>
     <t>215-21-02-001-018</t>
   </si>
   <si>
@@ -266,15 +338,12 @@
     <t>215-21-02-001-047-000</t>
   </si>
   <si>
-    <t>10021</t>
+    <t>215-21-02-001-999</t>
   </si>
   <si>
     <t>BONIFICACION PROFESOR ENCARGADO ESC RURAL</t>
   </si>
   <si>
-    <t>215-21-02-001-999</t>
-  </si>
-  <si>
     <t>215-21-02-001-999-000</t>
   </si>
   <si>
@@ -299,6 +368,36 @@
     <t>BRP MENCION</t>
   </si>
   <si>
+    <t>10047</t>
+  </si>
+  <si>
+    <t>RETROACTIVO BRP TITULO</t>
+  </si>
+  <si>
+    <t>10048</t>
+  </si>
+  <si>
+    <t>RETROACTIVO BRP MENCION</t>
+  </si>
+  <si>
+    <t>10049</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIGNACION DE TRAMO</t>
+  </si>
+  <si>
+    <t>10051</t>
+  </si>
+  <si>
+    <t>DIFERENCIA ASIG. TRAMO</t>
+  </si>
+  <si>
+    <t>10052</t>
+  </si>
+  <si>
+    <t>DIFERENCIA ASIG. PRIORITARIO</t>
+  </si>
+  <si>
     <t>215-21-02-005-003</t>
   </si>
   <si>
@@ -320,10 +419,10 @@
     <t>215-21-02-001-004</t>
   </si>
   <si>
-    <t>10080</t>
-  </si>
-  <si>
-    <t>DIFERENCIA BIENIOS</t>
+    <t>215-21-02-001-001-000</t>
+  </si>
+  <si>
+    <t>215-21-02-001-044</t>
   </si>
   <si>
     <t>10081</t>
@@ -332,15 +431,21 @@
     <t>RETROACTIVO ASIGNACION DE EXPERIENCIA</t>
   </si>
   <si>
-    <t>110</t>
+    <t>10085</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIG ASIG ALUM PRIORITARIOS</t>
+  </si>
+  <si>
+    <t>10087</t>
+  </si>
+  <si>
+    <t>SNED DOCENTES</t>
   </si>
   <si>
     <t>R.B.M.N.</t>
   </si>
   <si>
-    <t>215-21-02-001-001-000</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -359,6 +464,12 @@
     <t>122</t>
   </si>
   <si>
+    <t>215-21-02-005-002</t>
+  </si>
+  <si>
+    <t>215-21-02-005-004</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
@@ -440,12 +551,30 @@
     <t>215-21-01-001-004</t>
   </si>
   <si>
+    <t>10077</t>
+  </si>
+  <si>
+    <t>RETRO REAJUSTE BONIF PROF ENCARGADO (ENERO)</t>
+  </si>
+  <si>
+    <t>10088</t>
+  </si>
+  <si>
+    <t>ADECO</t>
+  </si>
+  <si>
     <t>215-21-01-001-001-000</t>
   </si>
   <si>
     <t>215-21-01-001-050-000</t>
   </si>
   <si>
+    <t>215-21-01-005-002</t>
+  </si>
+  <si>
+    <t>215-21-01-005-004</t>
+  </si>
+  <si>
     <t>215-21-01-001-047</t>
   </si>
   <si>
@@ -485,36 +614,33 @@
     <t>FONDO DE PENSIÓN</t>
   </si>
   <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>CAJA LOS ANDES</t>
+  </si>
+  <si>
+    <t>COOPEUCH</t>
+  </si>
+  <si>
     <t>ANDESCOOP LTDA.</t>
   </si>
   <si>
-    <t>10003</t>
-  </si>
-  <si>
     <t>C.C.A.F. LOS ANDES</t>
   </si>
   <si>
-    <t>10004</t>
-  </si>
-  <si>
     <t>COLEGIO DE PROFESORES</t>
   </si>
   <si>
     <t>FALP</t>
   </si>
   <si>
-    <t>10006</t>
-  </si>
-  <si>
-    <t>COOPEUCH</t>
-  </si>
-  <si>
-    <t>10008</t>
-  </si>
-  <si>
     <t>FULL AHORRO</t>
   </si>
   <si>
+    <t>ASOCIACION DE JARDINES</t>
+  </si>
+  <si>
     <t>CHILENA CONSOLIDADA</t>
   </si>
   <si>
@@ -527,6 +653,9 @@
     <t>SECURITY PREVISION</t>
   </si>
   <si>
+    <t>HOGAR DE CRISTO</t>
+  </si>
+  <si>
     <t>10018</t>
   </si>
   <si>
@@ -563,6 +692,12 @@
     <t>REINTEGRO ASIG EXPERIENCIA 21109</t>
   </si>
   <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>DIAS AUSENTISMO MES ANTERIOR</t>
+  </si>
+  <si>
     <t>1004</t>
   </si>
   <si>
@@ -608,31 +743,28 @@
     <t>LIQUIDO A PAGO</t>
   </si>
   <si>
-    <t>1. Completa o corrige la columna cuenta_contable en la hoja CompletarAqui.</t>
-  </si>
-  <si>
-    <t>2. Si aparece un haber o descuento nuevo, vuelve a ejecutar el script: se agregará como COMPLETAR.</t>
-  </si>
-  <si>
-    <t>3. Si prefieres trabajar en CSV, este Excel se regenera desde mapeo_cuentas.csv.</t>
-  </si>
-  <si>
-    <t>4. La cuenta_presupuestaria_sugerida fue precargada desde Cuentas contables.pdf cuando fue posible.</t>
-  </si>
-  <si>
-    <t>215-21-02-005-002</t>
-  </si>
-  <si>
-    <t>215-21-02-005-004</t>
-  </si>
-  <si>
-    <t>215-21-01-005-002</t>
-  </si>
-  <si>
-    <t>215-21-01-005-004</t>
-  </si>
-  <si>
-    <t>215-21-02-001-044</t>
+    <t>Este archivo es el MAPEO MAESTRO de cuentas contables. Sus entradas nunca se borran ni sobreescriben.</t>
+  </si>
+  <si>
+    <t>1. Completa la columna cuenta_contable en filas con estado COMPLETAR y guarda este archivo.</t>
+  </si>
+  <si>
+    <t>2. Al procesar un nuevo mes, solo se agregan filas nuevas (códigos no vistos antes). Las existentes no cambian.</t>
+  </si>
+  <si>
+    <t>3. Si un código cambia de cuenta contable, edita directamente la fila correspondiente en este archivo.</t>
+  </si>
+  <si>
+    <t>4. La cuenta_presupuestaria_sugerida se precarga automáticamente cuando se detecta en archivos de referencia.</t>
+  </si>
+  <si>
+    <t>215-21-01-001-051</t>
+  </si>
+  <si>
+    <t>215-21-02-001-049</t>
+  </si>
+  <si>
+    <t>215-21-01-003-002</t>
   </si>
 </sst>
 </file>
@@ -651,7 +783,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -979,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1159,10 +1290,7 @@
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="I6" t="s">
         <v>27</v>
@@ -1188,7 +1316,7 @@
         <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -1211,19 +1339,19 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1275,7 +1403,10 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -1283,7 +1414,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1301,7 +1432,7 @@
         <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="I11" t="s">
         <v>38</v>
@@ -1327,7 +1458,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -1379,7 +1510,7 @@
         <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
         <v>44</v>
@@ -1405,7 +1536,7 @@
         <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
@@ -1431,7 +1562,7 @@
         <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1439,7 +1570,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -1457,7 +1588,7 @@
         <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" t="s">
         <v>50</v>
@@ -1465,7 +1596,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
@@ -1483,7 +1614,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I18" t="s">
         <v>52</v>
@@ -1491,7 +1622,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -1509,7 +1640,7 @@
         <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
         <v>54</v>
@@ -1517,7 +1648,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -1535,10 +1666,7 @@
         <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="I20" t="s">
         <v>56</v>
@@ -1546,7 +1674,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -1558,21 +1686,21 @@
         <v>13</v>
       </c>
       <c r="E21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
         <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -1584,21 +1712,21 @@
         <v>13</v>
       </c>
       <c r="E22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" t="s">
         <v>60</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1610,19 +1738,16 @@
         <v>13</v>
       </c>
       <c r="E23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s">
         <v>62</v>
       </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
       <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
+        <v>245</v>
       </c>
       <c r="I23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1639,19 +1764,19 @@
         <v>13</v>
       </c>
       <c r="E24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
         <v>65</v>
       </c>
-      <c r="G24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s">
-        <v>17</v>
-      </c>
       <c r="I24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1676,9 +1801,6 @@
       <c r="G25" t="s">
         <v>17</v>
       </c>
-      <c r="H25" t="s">
-        <v>17</v>
-      </c>
       <c r="I25" t="s">
         <v>67</v>
       </c>
@@ -1705,9 +1827,6 @@
       <c r="G26" t="s">
         <v>17</v>
       </c>
-      <c r="H26" t="s">
-        <v>17</v>
-      </c>
       <c r="I26" t="s">
         <v>69</v>
       </c>
@@ -1752,19 +1871,22 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
         <v>72</v>
       </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -1778,22 +1900,22 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s">
         <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I29" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -1807,27 +1929,27 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
         <v>77</v>
       </c>
-      <c r="F30" t="s">
-        <v>78</v>
-      </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -1836,19 +1958,22 @@
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>17</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -1862,19 +1987,16 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
         <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
         <v>81</v>
@@ -1891,22 +2013,19 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
         <v>82</v>
-      </c>
-      <c r="H33" t="s">
-        <v>83</v>
-      </c>
-      <c r="I33" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -1920,19 +2039,19 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -1946,19 +2065,19 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1972,19 +2091,19 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1998,19 +2117,19 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -2024,19 +2143,19 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -2050,24 +2169,24 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -2076,24 +2195,24 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2102,24 +2221,24 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>202</v>
+        <v>65</v>
       </c>
       <c r="I41" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -2128,24 +2247,24 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="G42" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -2154,19 +2273,19 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G43" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -2180,22 +2299,19 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="G44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H44" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2209,22 +2325,19 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
         <v>72</v>
       </c>
-      <c r="E45" t="s">
-        <v>105</v>
-      </c>
       <c r="F45" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2238,22 +2351,19 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E46" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>88</v>
-      </c>
-      <c r="H46" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -2267,27 +2377,24 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F47" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s">
-        <v>88</v>
-      </c>
-      <c r="H47" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -2296,24 +2403,24 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E48" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -2322,19 +2429,19 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -2348,22 +2455,22 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E50" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F50" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H50" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="I50" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -2377,22 +2484,22 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E51" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F51" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G51" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="H51" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I51" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -2406,22 +2513,19 @@
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E52" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F52" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="G52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H52" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I52" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2435,22 +2539,22 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="G53" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H53" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I53" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -2464,22 +2568,22 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E54" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="G54" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H54" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I54" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2493,22 +2597,19 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="F55" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="G55" t="s">
-        <v>118</v>
-      </c>
-      <c r="H55" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I55" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2522,24 +2623,24 @@
         <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
@@ -2548,27 +2649,24 @@
         <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>121</v>
-      </c>
-      <c r="H57" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
@@ -2577,27 +2675,24 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>123</v>
-      </c>
-      <c r="H58" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="I58" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
@@ -2606,27 +2701,24 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H59" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="I59" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
@@ -2635,27 +2727,24 @@
         <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F60" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
-        <v>127</v>
-      </c>
-      <c r="H60" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="I60" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
@@ -2664,27 +2753,24 @@
         <v>12</v>
       </c>
       <c r="D61" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" t="s">
         <v>120</v>
       </c>
-      <c r="E61" t="s">
-        <v>26</v>
-      </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="G61" t="s">
-        <v>123</v>
-      </c>
-      <c r="H61" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I61" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
@@ -2693,22 +2779,19 @@
         <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E62" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F62" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G62" t="s">
-        <v>125</v>
-      </c>
-      <c r="H62" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I62" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -2722,22 +2805,19 @@
         <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E63" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G63" t="s">
-        <v>125</v>
-      </c>
-      <c r="H63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I63" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -2751,22 +2831,19 @@
         <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E64" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="G64" t="s">
-        <v>125</v>
-      </c>
-      <c r="H64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I64" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -2780,27 +2857,24 @@
         <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
-        <v>123</v>
-      </c>
-      <c r="H65" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I65" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
@@ -2809,19 +2883,19 @@
         <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="G66" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -2835,19 +2909,19 @@
         <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G67" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I67" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2861,19 +2935,19 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F68" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G68" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -2887,19 +2961,19 @@
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="G69" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I69" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2913,24 +2987,24 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="F70" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="G70" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I70" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
@@ -2939,24 +3013,24 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F71" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G71" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I71" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -2965,27 +3039,24 @@
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="F72" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="G72" t="s">
-        <v>138</v>
-      </c>
-      <c r="H72" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="I72" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -2994,22 +3065,19 @@
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E73" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="F73" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="G73" t="s">
+        <v>245</v>
+      </c>
+      <c r="I73" t="s">
         <v>138</v>
-      </c>
-      <c r="H73" t="s">
-        <v>138</v>
-      </c>
-      <c r="I73" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -3023,22 +3091,22 @@
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F74" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="G74" t="s">
+        <v>131</v>
+      </c>
+      <c r="H74" t="s">
+        <v>131</v>
+      </c>
+      <c r="I74" t="s">
         <v>139</v>
-      </c>
-      <c r="H74" t="s">
-        <v>139</v>
-      </c>
-      <c r="I74" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -3052,27 +3120,27 @@
         <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E75" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F75" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="G75" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H75" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I75" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
@@ -3081,24 +3149,27 @@
         <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E76" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G76" t="s">
-        <v>200</v>
+        <v>111</v>
+      </c>
+      <c r="H76" t="s">
+        <v>144</v>
       </c>
       <c r="I76" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
@@ -3107,19 +3178,22 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E77" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="F77" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="G77" t="s">
-        <v>201</v>
+        <v>111</v>
+      </c>
+      <c r="H77" t="s">
+        <v>144</v>
       </c>
       <c r="I77" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -3133,22 +3207,19 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="G78" t="s">
-        <v>140</v>
-      </c>
-      <c r="H78" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I78" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -3162,22 +3233,19 @@
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E79" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="F79" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="G79" t="s">
-        <v>142</v>
-      </c>
-      <c r="H79" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I79" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -3191,22 +3259,22 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E80" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="F80" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="G80" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I80" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -3220,22 +3288,22 @@
         <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E81" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="F81" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="G81" t="s">
+        <v>154</v>
+      </c>
+      <c r="H81" t="s">
         <v>144</v>
       </c>
-      <c r="H81" t="s">
-        <v>145</v>
-      </c>
       <c r="I81" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -3249,22 +3317,22 @@
         <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F82" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G82" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H82" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="I82" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -3278,22 +3346,22 @@
         <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E83" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F83" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H83" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="I83" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -3307,24 +3375,27 @@
         <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F84" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s">
-        <v>20</v>
+        <v>155</v>
+      </c>
+      <c r="H84" t="s">
+        <v>156</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -3333,19 +3404,22 @@
         <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="E85" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F85" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>155</v>
+      </c>
+      <c r="H85" t="s">
+        <v>156</v>
       </c>
       <c r="I85" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -3359,24 +3433,24 @@
         <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E86" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="F86" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
@@ -3385,19 +3459,22 @@
         <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E87" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="G87" t="s">
-        <v>16</v>
+        <v>158</v>
+      </c>
+      <c r="H87" t="s">
+        <v>159</v>
       </c>
       <c r="I87" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
@@ -3411,22 +3488,22 @@
         <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F88" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="I88" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
@@ -3440,22 +3517,22 @@
         <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E89" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="I89" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -3469,22 +3546,22 @@
         <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E90" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F90" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G90" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="H90" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="I90" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
@@ -3498,27 +3575,27 @@
         <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E91" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="H91" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="I91" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
@@ -3527,24 +3604,27 @@
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E92" t="s">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="F92" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>162</v>
+      </c>
+      <c r="H92" t="s">
+        <v>163</v>
       </c>
       <c r="I92" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
@@ -3553,19 +3633,22 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E93" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F93" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="G93" t="s">
-        <v>16</v>
+        <v>162</v>
+      </c>
+      <c r="H93" t="s">
+        <v>163</v>
       </c>
       <c r="I93" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
@@ -3579,22 +3662,22 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F94" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="H94" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="I94" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
@@ -3608,22 +3691,22 @@
         <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="F95" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="G95" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="H95" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="I95" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -3637,22 +3720,19 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F96" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
-      </c>
-      <c r="H96" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I96" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
@@ -3666,27 +3746,24 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E97" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="G97" t="s">
-        <v>16</v>
-      </c>
-      <c r="H97" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I97" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
@@ -3695,27 +3772,24 @@
         <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
-      </c>
-      <c r="H98" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I98" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -3724,114 +3798,123 @@
         <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E99" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="F99" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="G99" t="s">
-        <v>16</v>
-      </c>
-      <c r="H99" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I99" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>157</v>
       </c>
       <c r="E100" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="F100" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="G100" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="I100" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>148</v>
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>157</v>
       </c>
       <c r="E101" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G101" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="I101" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>148</v>
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>157</v>
       </c>
       <c r="E102" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="F102" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="G102" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="I102" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
+        <v>12</v>
+      </c>
+      <c r="D103" t="s">
+        <v>157</v>
       </c>
       <c r="E103" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="F103" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="G103" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="I103" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3839,22 +3922,25 @@
         <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>148</v>
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
+        <v>157</v>
       </c>
       <c r="E104" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F104" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="G104" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="I104" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
@@ -3862,45 +3948,51 @@
         <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D105" t="s">
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F105" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="G105" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="I105" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
+        <v>157</v>
       </c>
       <c r="E106" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F106" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G106" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I106" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -3908,114 +4000,129 @@
         <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>157</v>
       </c>
       <c r="E107" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="F107" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="G107" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="I107" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>157</v>
       </c>
       <c r="E108" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="F108" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="G108" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="I108" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
+        <v>157</v>
       </c>
       <c r="E109" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F109" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="G109" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I109" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D110" t="s">
+        <v>157</v>
       </c>
       <c r="E110" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="F110" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="G110" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="I110" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D111" t="s">
+        <v>157</v>
       </c>
       <c r="E111" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="G111" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="I111" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
@@ -4023,68 +4130,77 @@
         <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>157</v>
       </c>
       <c r="E112" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F112" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="G112" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="I112" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
+        <v>157</v>
       </c>
       <c r="E113" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="F113" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="G113" t="s">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="I113" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
+        <v>157</v>
       </c>
       <c r="E114" t="s">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="G114" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
       <c r="I114" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
@@ -4092,22 +4208,28 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
+        <v>157</v>
       </c>
       <c r="E115" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="F115" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="G115" t="s">
-        <v>149</v>
+        <v>179</v>
+      </c>
+      <c r="H115" t="s">
+        <v>179</v>
       </c>
       <c r="I115" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -4115,22 +4237,28 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D116" t="s">
+        <v>157</v>
       </c>
       <c r="E116" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F116" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="G116" t="s">
-        <v>149</v>
+        <v>179</v>
+      </c>
+      <c r="H116" t="s">
+        <v>179</v>
       </c>
       <c r="I116" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -4138,22 +4266,28 @@
         <v>10</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D117" t="s">
+        <v>157</v>
       </c>
       <c r="E117" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="F117" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="G117" t="s">
-        <v>149</v>
+        <v>180</v>
+      </c>
+      <c r="H117" t="s">
+        <v>180</v>
       </c>
       <c r="I117" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
@@ -4161,22 +4295,28 @@
         <v>10</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D118" t="s">
+        <v>157</v>
       </c>
       <c r="E118" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F118" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="G118" t="s">
-        <v>149</v>
+        <v>180</v>
+      </c>
+      <c r="H118" t="s">
+        <v>180</v>
       </c>
       <c r="I118" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4184,22 +4324,25 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>157</v>
       </c>
       <c r="E119" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="F119" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="G119" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="I119" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
@@ -4207,45 +4350,54 @@
         <v>10</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D120" t="s">
+        <v>157</v>
       </c>
       <c r="E120" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="F120" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="G120" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="I120" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D121" t="s">
+        <v>157</v>
       </c>
       <c r="E121" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F121" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="G121" t="s">
+        <v>183</v>
+      </c>
+      <c r="H121" t="s">
+        <v>184</v>
+      </c>
+      <c r="I121" t="s">
         <v>149</v>
-      </c>
-      <c r="I121" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
@@ -4253,22 +4405,28 @@
         <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>157</v>
       </c>
       <c r="E122" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="F122" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="G122" t="s">
-        <v>149</v>
+        <v>185</v>
+      </c>
+      <c r="H122" t="s">
+        <v>186</v>
       </c>
       <c r="I122" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4276,22 +4434,28 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>157</v>
       </c>
       <c r="E123" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="F123" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="G123" t="s">
-        <v>149</v>
+        <v>187</v>
+      </c>
+      <c r="H123" t="s">
+        <v>188</v>
       </c>
       <c r="I123" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
@@ -4299,22 +4463,28 @@
         <v>10</v>
       </c>
       <c r="B124" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D124" t="s">
+        <v>157</v>
       </c>
       <c r="E124" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="F124" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s">
-        <v>149</v>
+        <v>187</v>
+      </c>
+      <c r="H124" t="s">
+        <v>188</v>
       </c>
       <c r="I124" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
@@ -4322,22 +4492,28 @@
         <v>10</v>
       </c>
       <c r="B125" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C125" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>157</v>
       </c>
       <c r="E125" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="F125" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="G125" t="s">
-        <v>149</v>
+        <v>187</v>
+      </c>
+      <c r="H125" t="s">
+        <v>188</v>
       </c>
       <c r="I125" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
@@ -4345,22 +4521,28 @@
         <v>10</v>
       </c>
       <c r="B126" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>157</v>
       </c>
       <c r="E126" t="s">
+        <v>78</v>
+      </c>
+      <c r="F126" t="s">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s">
         <v>187</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H126" t="s">
         <v>188</v>
       </c>
-      <c r="G126" t="s">
-        <v>149</v>
-      </c>
       <c r="I126" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
@@ -4368,22 +4550,25 @@
         <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>150</v>
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
+        <v>189</v>
       </c>
       <c r="E127" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="F127" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="G127" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="I127" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -4391,33 +4576,1440 @@
         <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
+        <v>189</v>
+      </c>
+      <c r="E128" t="s">
+        <v>98</v>
+      </c>
+      <c r="F128" t="s">
+        <v>88</v>
+      </c>
+      <c r="G128" t="s">
+        <v>16</v>
+      </c>
+      <c r="I128" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>189</v>
+      </c>
+      <c r="E129" t="s">
+        <v>114</v>
+      </c>
+      <c r="F129" t="s">
+        <v>115</v>
+      </c>
+      <c r="G129" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
+        <v>189</v>
+      </c>
+      <c r="E130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F130" t="s">
+        <v>119</v>
+      </c>
+      <c r="G130" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" t="s">
+        <v>189</v>
+      </c>
+      <c r="E131" t="s">
+        <v>37</v>
+      </c>
+      <c r="F131" t="s">
+        <v>38</v>
+      </c>
+      <c r="G131" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" t="s">
+        <v>189</v>
+      </c>
+      <c r="E132" t="s">
+        <v>51</v>
+      </c>
+      <c r="F132" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>10</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" t="s">
+        <v>128</v>
+      </c>
+      <c r="F133" t="s">
+        <v>129</v>
+      </c>
+      <c r="G133" t="s">
+        <v>16</v>
+      </c>
+      <c r="I133" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" t="s">
+        <v>189</v>
+      </c>
+      <c r="E134" t="s">
+        <v>53</v>
+      </c>
+      <c r="F134" t="s">
+        <v>54</v>
+      </c>
+      <c r="G134" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>10</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" t="s">
+        <v>189</v>
+      </c>
+      <c r="E135" t="s">
+        <v>133</v>
+      </c>
+      <c r="F135" t="s">
+        <v>134</v>
+      </c>
+      <c r="G135" t="s">
+        <v>16</v>
+      </c>
+      <c r="I135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" t="s">
+        <v>189</v>
+      </c>
+      <c r="E136" t="s">
+        <v>135</v>
+      </c>
+      <c r="F136" t="s">
+        <v>136</v>
+      </c>
+      <c r="G136" t="s">
+        <v>16</v>
+      </c>
+      <c r="I136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" t="s">
+        <v>189</v>
+      </c>
+      <c r="E137" t="s">
+        <v>137</v>
+      </c>
+      <c r="F137" t="s">
+        <v>138</v>
+      </c>
+      <c r="G137" t="s">
+        <v>16</v>
+      </c>
+      <c r="I137" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" t="s">
+        <v>189</v>
+      </c>
+      <c r="E138" t="s">
+        <v>94</v>
+      </c>
+      <c r="F138" t="s">
+        <v>139</v>
+      </c>
+      <c r="G138" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" t="s">
+        <v>189</v>
+      </c>
+      <c r="E139" t="s">
+        <v>140</v>
+      </c>
+      <c r="F139" t="s">
+        <v>141</v>
+      </c>
+      <c r="G139" t="s">
+        <v>16</v>
+      </c>
+      <c r="H139" t="s">
+        <v>16</v>
+      </c>
+      <c r="I139" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>10</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" t="s">
+        <v>189</v>
+      </c>
+      <c r="E140" t="s">
+        <v>143</v>
+      </c>
+      <c r="F140" t="s">
+        <v>110</v>
+      </c>
+      <c r="G140" t="s">
+        <v>16</v>
+      </c>
+      <c r="H140" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>10</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" t="s">
+        <v>189</v>
+      </c>
+      <c r="E141" t="s">
+        <v>145</v>
+      </c>
+      <c r="F141" t="s">
+        <v>113</v>
+      </c>
+      <c r="G141" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" t="s">
+        <v>189</v>
+      </c>
+      <c r="E142" t="s">
+        <v>66</v>
+      </c>
+      <c r="F142" t="s">
+        <v>67</v>
+      </c>
+      <c r="G142" t="s">
+        <v>16</v>
+      </c>
+      <c r="I142" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>10</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" t="s">
+        <v>189</v>
+      </c>
+      <c r="E143" t="s">
+        <v>68</v>
+      </c>
+      <c r="F143" t="s">
+        <v>69</v>
+      </c>
+      <c r="G143" t="s">
+        <v>16</v>
+      </c>
+      <c r="I143" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" t="s">
+        <v>189</v>
+      </c>
+      <c r="E144" t="s">
+        <v>148</v>
+      </c>
+      <c r="F144" t="s">
+        <v>149</v>
+      </c>
+      <c r="G144" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>10</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" t="s">
+        <v>189</v>
+      </c>
+      <c r="E145" t="s">
+        <v>152</v>
+      </c>
+      <c r="F145" t="s">
+        <v>153</v>
+      </c>
+      <c r="G145" t="s">
+        <v>16</v>
+      </c>
+      <c r="H145" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>10</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" t="s">
+        <v>70</v>
+      </c>
+      <c r="F146" t="s">
+        <v>71</v>
+      </c>
+      <c r="G146" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" t="s">
+        <v>16</v>
+      </c>
+      <c r="I146" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>10</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" t="s">
+        <v>189</v>
+      </c>
+      <c r="E147" t="s">
+        <v>74</v>
+      </c>
+      <c r="F147" t="s">
+        <v>75</v>
+      </c>
+      <c r="G147" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" t="s">
+        <v>189</v>
+      </c>
+      <c r="E148" t="s">
+        <v>76</v>
+      </c>
+      <c r="F148" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" t="s">
+        <v>16</v>
+      </c>
+      <c r="H148" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>10</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" t="s">
+        <v>189</v>
+      </c>
+      <c r="E149" t="s">
+        <v>78</v>
+      </c>
+      <c r="F149" t="s">
+        <v>79</v>
+      </c>
+      <c r="G149" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>10</v>
+      </c>
+      <c r="B150" t="s">
+        <v>190</v>
+      </c>
+      <c r="C150" t="s">
         <v>191</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E150" t="s">
+        <v>70</v>
+      </c>
+      <c r="F150" t="s">
+        <v>71</v>
+      </c>
+      <c r="G150" t="s">
         <v>192</v>
       </c>
-      <c r="F128" t="s">
+      <c r="I150" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>10</v>
+      </c>
+      <c r="B151" t="s">
+        <v>190</v>
+      </c>
+      <c r="C151" t="s">
+        <v>191</v>
+      </c>
+      <c r="E151" t="s">
+        <v>72</v>
+      </c>
+      <c r="F151" t="s">
+        <v>73</v>
+      </c>
+      <c r="G151" t="s">
+        <v>192</v>
+      </c>
+      <c r="I151" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>10</v>
+      </c>
+      <c r="B152" t="s">
+        <v>190</v>
+      </c>
+      <c r="C152" t="s">
+        <v>191</v>
+      </c>
+      <c r="E152" t="s">
+        <v>74</v>
+      </c>
+      <c r="F152" t="s">
+        <v>75</v>
+      </c>
+      <c r="G152" t="s">
+        <v>192</v>
+      </c>
+      <c r="I152" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>10</v>
+      </c>
+      <c r="B153" t="s">
+        <v>190</v>
+      </c>
+      <c r="C153" t="s">
+        <v>191</v>
+      </c>
+      <c r="E153" t="s">
+        <v>95</v>
+      </c>
+      <c r="F153" t="s">
+        <v>77</v>
+      </c>
+      <c r="G153" t="s">
+        <v>192</v>
+      </c>
+      <c r="I153" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>10</v>
+      </c>
+      <c r="B154" t="s">
+        <v>190</v>
+      </c>
+      <c r="C154" t="s">
+        <v>191</v>
+      </c>
+      <c r="E154" t="s">
+        <v>96</v>
+      </c>
+      <c r="F154" t="s">
+        <v>79</v>
+      </c>
+      <c r="G154" t="s">
+        <v>192</v>
+      </c>
+      <c r="I154" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>10</v>
+      </c>
+      <c r="B155" t="s">
+        <v>190</v>
+      </c>
+      <c r="C155" t="s">
+        <v>191</v>
+      </c>
+      <c r="E155" t="s">
+        <v>76</v>
+      </c>
+      <c r="F155" t="s">
+        <v>77</v>
+      </c>
+      <c r="G155" t="s">
+        <v>192</v>
+      </c>
+      <c r="I155" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>10</v>
+      </c>
+      <c r="B156" t="s">
+        <v>190</v>
+      </c>
+      <c r="C156" t="s">
+        <v>191</v>
+      </c>
+      <c r="E156" t="s">
+        <v>78</v>
+      </c>
+      <c r="F156" t="s">
+        <v>79</v>
+      </c>
+      <c r="G156" t="s">
+        <v>192</v>
+      </c>
+      <c r="I156" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>10</v>
+      </c>
+      <c r="B157" t="s">
+        <v>190</v>
+      </c>
+      <c r="C157" t="s">
         <v>193</v>
       </c>
-      <c r="G128" t="s">
-        <v>149</v>
-      </c>
-      <c r="I128" t="s">
+      <c r="E157" t="s">
+        <v>194</v>
+      </c>
+      <c r="F157" t="s">
+        <v>195</v>
+      </c>
+      <c r="G157" t="s">
+        <v>192</v>
+      </c>
+      <c r="I157" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>10</v>
+      </c>
+      <c r="B158" t="s">
+        <v>190</v>
+      </c>
+      <c r="C158" t="s">
         <v>193</v>
       </c>
+      <c r="E158" t="s">
+        <v>196</v>
+      </c>
+      <c r="F158" t="s">
+        <v>197</v>
+      </c>
+      <c r="G158" t="s">
+        <v>192</v>
+      </c>
+      <c r="I158" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>10</v>
+      </c>
+      <c r="B159" t="s">
+        <v>190</v>
+      </c>
+      <c r="C159" t="s">
+        <v>193</v>
+      </c>
+      <c r="E159" t="s">
+        <v>14</v>
+      </c>
+      <c r="F159" t="s">
+        <v>198</v>
+      </c>
+      <c r="G159" t="s">
+        <v>192</v>
+      </c>
+      <c r="I159" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160" t="s">
+        <v>190</v>
+      </c>
+      <c r="C160" t="s">
+        <v>193</v>
+      </c>
+      <c r="E160" t="s">
+        <v>18</v>
+      </c>
+      <c r="F160" t="s">
+        <v>199</v>
+      </c>
+      <c r="G160" t="s">
+        <v>192</v>
+      </c>
+      <c r="I160" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>10</v>
+      </c>
+      <c r="B161" t="s">
+        <v>190</v>
+      </c>
+      <c r="C161" t="s">
+        <v>193</v>
+      </c>
+      <c r="E161" t="s">
+        <v>83</v>
+      </c>
+      <c r="F161" t="s">
+        <v>200</v>
+      </c>
+      <c r="G161" t="s">
+        <v>192</v>
+      </c>
+      <c r="I161" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162" t="s">
+        <v>190</v>
+      </c>
+      <c r="C162" t="s">
+        <v>193</v>
+      </c>
+      <c r="E162" t="s">
+        <v>85</v>
+      </c>
+      <c r="F162" t="s">
+        <v>201</v>
+      </c>
+      <c r="G162" t="s">
+        <v>192</v>
+      </c>
+      <c r="I162" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>10</v>
+      </c>
+      <c r="B163" t="s">
+        <v>190</v>
+      </c>
+      <c r="C163" t="s">
+        <v>193</v>
+      </c>
+      <c r="E163" t="s">
+        <v>21</v>
+      </c>
+      <c r="F163" t="s">
+        <v>202</v>
+      </c>
+      <c r="G163" t="s">
+        <v>192</v>
+      </c>
+      <c r="I163" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164" t="s">
+        <v>190</v>
+      </c>
+      <c r="C164" t="s">
+        <v>193</v>
+      </c>
+      <c r="E164" t="s">
+        <v>86</v>
+      </c>
+      <c r="F164" t="s">
+        <v>198</v>
+      </c>
+      <c r="G164" t="s">
+        <v>192</v>
+      </c>
+      <c r="I164" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>10</v>
+      </c>
+      <c r="B165" t="s">
+        <v>190</v>
+      </c>
+      <c r="C165" t="s">
+        <v>193</v>
+      </c>
+      <c r="E165" t="s">
+        <v>87</v>
+      </c>
+      <c r="F165" t="s">
+        <v>203</v>
+      </c>
+      <c r="G165" t="s">
+        <v>192</v>
+      </c>
+      <c r="I165" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166" t="s">
+        <v>190</v>
+      </c>
+      <c r="C166" t="s">
+        <v>193</v>
+      </c>
+      <c r="E166" t="s">
+        <v>23</v>
+      </c>
+      <c r="F166" t="s">
+        <v>204</v>
+      </c>
+      <c r="G166" t="s">
+        <v>192</v>
+      </c>
+      <c r="I166" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" t="s">
+        <v>190</v>
+      </c>
+      <c r="C167" t="s">
+        <v>193</v>
+      </c>
+      <c r="E167" t="s">
+        <v>101</v>
+      </c>
+      <c r="F167" t="s">
+        <v>205</v>
+      </c>
+      <c r="G167" t="s">
+        <v>192</v>
+      </c>
+      <c r="I167" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168" t="s">
+        <v>190</v>
+      </c>
+      <c r="C168" t="s">
+        <v>193</v>
+      </c>
+      <c r="E168" t="s">
+        <v>206</v>
+      </c>
+      <c r="F168" t="s">
+        <v>207</v>
+      </c>
+      <c r="G168" t="s">
+        <v>192</v>
+      </c>
+      <c r="I168" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169" t="s">
+        <v>190</v>
+      </c>
+      <c r="C169" t="s">
+        <v>193</v>
+      </c>
+      <c r="E169" t="s">
+        <v>28</v>
+      </c>
+      <c r="F169" t="s">
+        <v>208</v>
+      </c>
+      <c r="G169" t="s">
+        <v>192</v>
+      </c>
+      <c r="I169" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170" t="s">
+        <v>190</v>
+      </c>
+      <c r="C170" t="s">
+        <v>193</v>
+      </c>
+      <c r="E170" t="s">
+        <v>166</v>
+      </c>
+      <c r="F170" t="s">
+        <v>209</v>
+      </c>
+      <c r="G170" t="s">
+        <v>192</v>
+      </c>
+      <c r="I170" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171" t="s">
+        <v>190</v>
+      </c>
+      <c r="C171" t="s">
+        <v>193</v>
+      </c>
+      <c r="E171" t="s">
+        <v>210</v>
+      </c>
+      <c r="F171" t="s">
+        <v>211</v>
+      </c>
+      <c r="G171" t="s">
+        <v>192</v>
+      </c>
+      <c r="I171" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>10</v>
+      </c>
+      <c r="B172" t="s">
+        <v>190</v>
+      </c>
+      <c r="C172" t="s">
+        <v>193</v>
+      </c>
+      <c r="E172" t="s">
+        <v>212</v>
+      </c>
+      <c r="F172" t="s">
+        <v>213</v>
+      </c>
+      <c r="G172" t="s">
+        <v>192</v>
+      </c>
+      <c r="I172" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>10</v>
+      </c>
+      <c r="B173" t="s">
+        <v>190</v>
+      </c>
+      <c r="C173" t="s">
+        <v>193</v>
+      </c>
+      <c r="E173" t="s">
+        <v>30</v>
+      </c>
+      <c r="F173" t="s">
+        <v>214</v>
+      </c>
+      <c r="G173" t="s">
+        <v>192</v>
+      </c>
+      <c r="I173" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174" t="s">
+        <v>190</v>
+      </c>
+      <c r="C174" t="s">
+        <v>193</v>
+      </c>
+      <c r="E174" t="s">
+        <v>90</v>
+      </c>
+      <c r="F174" t="s">
+        <v>215</v>
+      </c>
+      <c r="G174" t="s">
+        <v>192</v>
+      </c>
+      <c r="I174" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>10</v>
+      </c>
+      <c r="B175" t="s">
+        <v>190</v>
+      </c>
+      <c r="C175" t="s">
+        <v>193</v>
+      </c>
+      <c r="E175" t="s">
+        <v>216</v>
+      </c>
+      <c r="F175" t="s">
+        <v>217</v>
+      </c>
+      <c r="G175" t="s">
+        <v>192</v>
+      </c>
+      <c r="I175" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>10</v>
+      </c>
+      <c r="B176" t="s">
+        <v>190</v>
+      </c>
+      <c r="C176" t="s">
+        <v>193</v>
+      </c>
+      <c r="E176" t="s">
+        <v>218</v>
+      </c>
+      <c r="F176" t="s">
+        <v>219</v>
+      </c>
+      <c r="G176" t="s">
+        <v>192</v>
+      </c>
+      <c r="I176" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177" t="s">
+        <v>190</v>
+      </c>
+      <c r="C177" t="s">
+        <v>193</v>
+      </c>
+      <c r="E177" t="s">
+        <v>220</v>
+      </c>
+      <c r="F177" t="s">
+        <v>221</v>
+      </c>
+      <c r="G177" t="s">
+        <v>192</v>
+      </c>
+      <c r="I177" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>25</v>
+      </c>
+      <c r="B178" t="s">
+        <v>190</v>
+      </c>
+      <c r="C178" t="s">
+        <v>193</v>
+      </c>
+      <c r="E178" t="s">
+        <v>222</v>
+      </c>
+      <c r="F178" t="s">
+        <v>223</v>
+      </c>
+      <c r="G178" t="s">
+        <v>192</v>
+      </c>
+      <c r="I178" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179" t="s">
+        <v>193</v>
+      </c>
+      <c r="E179" t="s">
+        <v>224</v>
+      </c>
+      <c r="F179" t="s">
+        <v>225</v>
+      </c>
+      <c r="G179" t="s">
+        <v>192</v>
+      </c>
+      <c r="I179" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B180" t="s">
+        <v>190</v>
+      </c>
+      <c r="C180" t="s">
+        <v>193</v>
+      </c>
+      <c r="E180" t="s">
+        <v>226</v>
+      </c>
+      <c r="F180" t="s">
+        <v>227</v>
+      </c>
+      <c r="G180" t="s">
+        <v>192</v>
+      </c>
+      <c r="I180" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181" t="s">
+        <v>190</v>
+      </c>
+      <c r="C181" t="s">
+        <v>193</v>
+      </c>
+      <c r="E181" t="s">
+        <v>228</v>
+      </c>
+      <c r="F181" t="s">
+        <v>229</v>
+      </c>
+      <c r="G181" t="s">
+        <v>192</v>
+      </c>
+      <c r="I181" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182" t="s">
+        <v>190</v>
+      </c>
+      <c r="C182" t="s">
+        <v>193</v>
+      </c>
+      <c r="E182" t="s">
+        <v>230</v>
+      </c>
+      <c r="F182" t="s">
+        <v>231</v>
+      </c>
+      <c r="G182" t="s">
+        <v>192</v>
+      </c>
+      <c r="I182" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183" t="s">
+        <v>190</v>
+      </c>
+      <c r="C183" t="s">
+        <v>193</v>
+      </c>
+      <c r="E183" t="s">
+        <v>232</v>
+      </c>
+      <c r="F183" t="s">
+        <v>233</v>
+      </c>
+      <c r="G183" t="s">
+        <v>192</v>
+      </c>
+      <c r="I183" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184" t="s">
+        <v>190</v>
+      </c>
+      <c r="C184" t="s">
+        <v>193</v>
+      </c>
+      <c r="E184" t="s">
+        <v>234</v>
+      </c>
+      <c r="F184" t="s">
+        <v>235</v>
+      </c>
+      <c r="G184" t="s">
+        <v>192</v>
+      </c>
+      <c r="I184" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>10</v>
+      </c>
+      <c r="B185" t="s">
+        <v>190</v>
+      </c>
+      <c r="C185" t="s">
+        <v>236</v>
+      </c>
+      <c r="E185" t="s">
+        <v>237</v>
+      </c>
+      <c r="F185" t="s">
+        <v>238</v>
+      </c>
+      <c r="G185" t="s">
+        <v>192</v>
+      </c>
+      <c r="I185" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J128" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J185" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4425,396 +6017,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010059ACE5E4BEA997428F384D77A572FD4B" ma:contentTypeVersion="25" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9f547c5695b7d64dd799e97a122c27b5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xmlns:ns3="02820edd-19e4-48e2-bbb8-afe73d8f445a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94869d0085d4c3d202e2705940597308" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="c3f36bf9-47a2-4bd6-a930-f0009ac4a680"/>
-    <xsd:import namespace="02820edd-19e4-48e2-bbb8-afe73d8f445a"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Temastratadosenlareuni_x00f3_n" minOccurs="0"/>
-                <xsd:element ref="ns2:ParticipantesdelaReuni_x00f3_n" minOccurs="0"/>
-                <xsd:element ref="ns2:NombreAutor_x002f_adelacta" minOccurs="0"/>
-                <xsd:element ref="ns2:CompromisosyAcuerdos" minOccurs="0"/>
-                <xsd:element ref="ns2:Nombredequienfirmaelacta" minOccurs="0"/>
-                <xsd:element ref="ns2:Fecha" minOccurs="0"/>
-                <xsd:element ref="ns2:Comuna" minOccurs="0"/>
-                <xsd:element ref="ns2:ModalidaddeReuni_x00f3_n" minOccurs="0"/>
-                <xsd:element ref="ns2:TitulodeReuni_x00f3_n" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="31" nillable="true" ma:displayName="Propiedades de la Directiva de cumplimiento unificado" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="32" nillable="true" ma:displayName="Acción de IU de la Directiva de cumplimiento unificado" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2c9ea187-b6c3-4edc-84ee-20ba49192b82" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Temastratadosenlareuni_x00f3_n" ma:index="19" nillable="true" ma:displayName="Temas tratados en la reunión" ma:internalName="Temastratadosenlareuni_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ParticipantesdelaReuni_x00f3_n" ma:index="20" nillable="true" ma:displayName="Participantes de la Reunión" ma:format="Dropdown" ma:internalName="ParticipantesdelaReuni_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="NombreAutor_x002f_adelacta" ma:index="21" nillable="true" ma:displayName="Nombre Autor/a del acta" ma:format="Dropdown" ma:internalName="NombreAutor_x002f_adelacta">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CompromisosyAcuerdos" ma:index="22" nillable="true" ma:displayName="Compromisos y Acuerdos" ma:format="Dropdown" ma:internalName="CompromisosyAcuerdos">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Nombredequienfirmaelacta" ma:index="23" nillable="true" ma:displayName="Nombre de quien firma el acta" ma:format="Dropdown" ma:internalName="Nombredequienfirmaelacta">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Fecha" ma:index="24" nillable="true" ma:displayName="Fecha" ma:format="DateOnly" ma:internalName="Fecha">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Comuna" ma:index="25" nillable="true" ma:displayName="Comuna" ma:format="Dropdown" ma:internalName="Comuna">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ModalidaddeReuni_x00f3_n" ma:index="26" nillable="true" ma:displayName="Modalidad de Reunión" ma:format="Dropdown" ma:internalName="ModalidaddeReuni_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TitulodeReuni_x00f3_n" ma:index="27" nillable="true" ma:displayName="Titulo de Reunión" ma:format="Dropdown" ma:internalName="TitulodeReuni_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="28" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="29" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="30" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="02820edd-19e4-48e2-bbb8-afe73d8f445a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cab5bc57-3100-459d-b5b6-8d669ebb1493}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="02820edd-19e4-48e2-bbb8-afe73d8f445a">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TitulodeReuni_x00f3_n xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <NombreAutor_x002f_adelacta xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <Fecha xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <Nombredequienfirmaelacta xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <ParticipantesdelaReuni_x00f3_n xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <CompromisosyAcuerdos xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <TaxCatchAll xmlns="02820edd-19e4-48e2-bbb8-afe73d8f445a" xsi:nil="true"/>
-    <Comuna xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Temastratadosenlareuni_x00f3_n xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <ModalidaddeReuni_x00f3_n xmlns="c3f36bf9-47a2-4bd6-a930-f0009ac4a680" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090F8BC0-5226-4BD8-B8AA-B54800B6AAC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="c3f36bf9-47a2-4bd6-a930-f0009ac4a680"/>
-    <ds:schemaRef ds:uri="02820edd-19e4-48e2-bbb8-afe73d8f445a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F370DBD6-5FB9-4B3D-A70E-559F8EBE1348}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3f36bf9-47a2-4bd6-a930-f0009ac4a680"/>
-    <ds:schemaRef ds:uri="02820edd-19e4-48e2-bbb8-afe73d8f445a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63AAFFBC-6701-4A80-AA04-49C34355BB1B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/mapeo_maestro.xlsx
+++ b/mapeo_maestro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sleppetorcagobcl-my.sharepoint.com/personal/wilson_rojas_sleppetorca_gob_cl/Documents/Proyecto Centralizacion Remuneraciones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_EA5C713F984F649B7B9FB954BD1AAC43572D4901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B76E983-31CF-49E8-B5F1-587EF3C1B6DB}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_8A469A8709BD2DE8C92F5C56AD4DF4057C6C8CBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB3B110-58E4-4C16-89D2-EBE2B8B587D3}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-3585" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,27 @@
     <sheet name="ComoUsarlo" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompletarAqui!$A$1:$J$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompletarAqui!$A$1:$J$328</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2640" uniqueCount="347">
   <si>
     <t>estado</t>
   </si>
@@ -89,52 +102,172 @@
     <t>114-06-00-000-000-000</t>
   </si>
   <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>ASIGNACION DE RESPONSABILIDAD</t>
+  </si>
+  <si>
+    <t>215-21-02-001-018</t>
+  </si>
+  <si>
     <t>10005</t>
   </si>
   <si>
     <t>ASIGNACION MOVILIZACION</t>
   </si>
   <si>
+    <t>10007</t>
+  </si>
+  <si>
     <t>10009</t>
   </si>
   <si>
     <t>PLANILLA SUPLEMENTARIA</t>
   </si>
   <si>
+    <t>10010</t>
+  </si>
+  <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>ASIGNACION MENSUAL ART 43 LEY 21109</t>
+  </si>
+  <si>
+    <t>10012</t>
+  </si>
+  <si>
+    <t>BONO ALTA CONCENTRACION NO DOCENTE</t>
+  </si>
+  <si>
+    <t>215-21-02-001-046</t>
+  </si>
+  <si>
+    <t>10013</t>
+  </si>
+  <si>
+    <t>BONO EXPERIENCIA LEY 21109</t>
+  </si>
+  <si>
+    <t>215-21-03-004-001-000</t>
+  </si>
+  <si>
+    <t>10014</t>
+  </si>
+  <si>
+    <t>ASIG RESPONSABILIDAD COORDINACION PIE</t>
+  </si>
+  <si>
+    <t>10016</t>
+  </si>
+  <si>
+    <t>SUELDO BASE</t>
+  </si>
+  <si>
+    <t>10017</t>
+  </si>
+  <si>
+    <t>BIENIOS ASISTENTES</t>
+  </si>
+  <si>
+    <t>215-21-02-001-044</t>
+  </si>
+  <si>
+    <t>10018</t>
+  </si>
+  <si>
+    <t>BONO LEY 19.464</t>
+  </si>
+  <si>
+    <t>10020</t>
+  </si>
+  <si>
+    <t>ASIGNACION DE EXPERIENCIA LEY 21109</t>
+  </si>
+  <si>
+    <t>10026</t>
+  </si>
+  <si>
+    <t>BONO ESPECIAL</t>
+  </si>
+  <si>
+    <t>10028</t>
+  </si>
+  <si>
+    <t>BONO DESEMPEÑO LABORAL (CUOTA 2)</t>
+  </si>
+  <si>
+    <t>10029</t>
+  </si>
+  <si>
+    <t>ART 42 TRANSITORIO FEBRERO (ASIG EXP PAPUDO)</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>RETRO ART 42 TRANSIT ENERO (ASIG EXP PAPUDO)</t>
+  </si>
+  <si>
+    <t>10031</t>
+  </si>
+  <si>
+    <t>RETRO ART 42 TRANSIT DICIEM (ASIG EXP PAPUDO)</t>
+  </si>
+  <si>
+    <t>10032</t>
+  </si>
+  <si>
+    <t>ASIG ALTA CONC DE ALUMNOS PRIORIT AAEE</t>
+  </si>
+  <si>
+    <t>10033</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE SUELDO BASE (ENERO)</t>
+  </si>
+  <si>
+    <t>10034</t>
+  </si>
+  <si>
+    <t>ASIG RESPONSABILIDAD PIE</t>
+  </si>
+  <si>
+    <t>10035</t>
+  </si>
+  <si>
+    <t>ART 13 LEY 21806</t>
+  </si>
+  <si>
+    <t>10036</t>
+  </si>
+  <si>
+    <t>10037</t>
+  </si>
+  <si>
+    <t>PLANILLA COMPLEMENTARIA (ART 42 T)</t>
+  </si>
+  <si>
+    <t>10038</t>
+  </si>
+  <si>
+    <t>BONO DE VACACIONES</t>
+  </si>
+  <si>
+    <t>10040</t>
+  </si>
+  <si>
+    <t>ASIG FAMILIAR</t>
+  </si>
+  <si>
     <t>COMPLETAR</t>
   </si>
   <si>
-    <t>10012</t>
-  </si>
-  <si>
-    <t>BONO ALTA CONCENTRACION NO DOCENTE</t>
-  </si>
-  <si>
-    <t>10014</t>
-  </si>
-  <si>
-    <t>ASIG RESPONSABILIDAD COORDINACION PIE</t>
-  </si>
-  <si>
-    <t>10020</t>
-  </si>
-  <si>
-    <t>ASIGNACION DE EXPERIENCIA LEY 21109</t>
-  </si>
-  <si>
-    <t>215-21-03-004-001-000</t>
-  </si>
-  <si>
-    <t>10036</t>
-  </si>
-  <si>
-    <t>ASIGNACION MENSUAL ART 43 LEY 21109</t>
-  </si>
-  <si>
-    <t>10037</t>
-  </si>
-  <si>
-    <t>PLANILLA COMPLEMENTARIA (ART 42 T)</t>
+    <t>10047</t>
+  </si>
+  <si>
+    <t>ART 42 TRANS ( ASIG EXP PAPUDO)</t>
   </si>
   <si>
     <t>10050</t>
@@ -146,9 +279,6 @@
     <t>10053</t>
   </si>
   <si>
-    <t>RETROACTIVO REAJUSTE SUELDO BASE (ENERO)</t>
-  </si>
-  <si>
     <t>10054</t>
   </si>
   <si>
@@ -158,15 +288,21 @@
     <t>10057</t>
   </si>
   <si>
-    <t>BONO ESPECIAL</t>
-  </si>
-  <si>
     <t>10058</t>
   </si>
   <si>
     <t>DIFERENCIA BONO DE VACACIONES</t>
   </si>
   <si>
+    <t>10059</t>
+  </si>
+  <si>
+    <t>DIFERENCIA AGUINALDO DE NAVIDAD</t>
+  </si>
+  <si>
+    <t>215-21-02-005-001</t>
+  </si>
+  <si>
     <t>10063</t>
   </si>
   <si>
@@ -185,6 +321,36 @@
     <t>DIFERENCIA SUELDO BASE</t>
   </si>
   <si>
+    <t>10066</t>
+  </si>
+  <si>
+    <t>RETROCTIVO ASIG MENSUAL ART 43 LEY 21109</t>
+  </si>
+  <si>
+    <t>10069</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE SUELDO BASE (DIC)</t>
+  </si>
+  <si>
+    <t>10070</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE ASIG RESP (ENERO)</t>
+  </si>
+  <si>
+    <t>10071</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE ASIG DE RESP (DIC)</t>
+  </si>
+  <si>
+    <t>10076</t>
+  </si>
+  <si>
+    <t>RETROACTIVO MOVILIZACION</t>
+  </si>
+  <si>
     <t>10079</t>
   </si>
   <si>
@@ -215,15 +381,30 @@
     <t>SNED ASISTENTES</t>
   </si>
   <si>
+    <t>215-21-02-001-049</t>
+  </si>
+  <si>
+    <t>10092</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIG FAMILIAR</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>SUELDO BASE</t>
-  </si>
-  <si>
     <t>215-21-03-004-000-000</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>BRP TITULO</t>
+  </si>
+  <si>
+    <t>215-21-02-001-048</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
@@ -254,12 +435,15 @@
     <t>(*) APORTE S.I.S.</t>
   </si>
   <si>
+    <t>32030</t>
+  </si>
+  <si>
+    <t>APORTE CAPITALIZACIÓN INDIVIDUAL</t>
+  </si>
+  <si>
     <t>32031</t>
   </si>
   <si>
-    <t>APORTE CAPITALIZACIÓN INDIVIDUAL</t>
-  </si>
-  <si>
     <t>32032</t>
   </si>
   <si>
@@ -275,25 +459,52 @@
     <t>ASIGNACION CARRERA DOCENTE PARVULARIA</t>
   </si>
   <si>
-    <t>10003</t>
-  </si>
-  <si>
     <t>INCREMENTO 5%</t>
   </si>
   <si>
     <t>10004</t>
   </si>
   <si>
+    <t>ART 33 LEY 21.724</t>
+  </si>
+  <si>
     <t>10006</t>
   </si>
   <si>
+    <t>BONO ART 33 LEY 21724</t>
+  </si>
+  <si>
     <t>10008</t>
   </si>
   <si>
-    <t>ASIGNACION DE RESPONSABILIDAD</t>
-  </si>
-  <si>
-    <t>10017</t>
+    <t>DIF. BONO INCENTIVO</t>
+  </si>
+  <si>
+    <t>DIF ART 13 LEY 21806</t>
+  </si>
+  <si>
+    <t>DIFERENCIAL BONO DE VACACIONES</t>
+  </si>
+  <si>
+    <t>215-21-02-005-003</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE S.BASE (DICIEMBRE)</t>
+  </si>
+  <si>
+    <t>10015</t>
+  </si>
+  <si>
+    <t>DIFERENCIA INCREMENTO</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE ASIG RESPO DIRECTIVA</t>
+  </si>
+  <si>
+    <t>10019</t>
+  </si>
+  <si>
+    <t>BONO DESEMPEÑO LABORAL (CUOTA 1)</t>
   </si>
   <si>
     <t>10021</t>
@@ -308,67 +519,88 @@
     <t>RETROACTIVO SUELDO BASE</t>
   </si>
   <si>
+    <t>10023</t>
+  </si>
+  <si>
+    <t>ASIG FAMILIAR RETROACTIVA</t>
+  </si>
+  <si>
+    <t>10024</t>
+  </si>
+  <si>
+    <t>RETROACTIVO BONO DE INCENTIVO</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>32029</t>
   </si>
   <si>
-    <t>32030</t>
-  </si>
-  <si>
     <t>CONTRATA</t>
   </si>
   <si>
-    <t>10007</t>
-  </si>
-  <si>
-    <t>215-21-02-001-018</t>
+    <t>ASIGNACION DE RESPONSABILIDAD DIRECTIVA</t>
   </si>
   <si>
     <t>215-21-02-001-018-000</t>
   </si>
   <si>
-    <t>10010</t>
-  </si>
-  <si>
-    <t>ASIGNACION DE RESPONSABILIDAD DIRECTIVA</t>
-  </si>
-  <si>
     <t>215-21-02-001-047-000</t>
   </si>
   <si>
     <t>215-21-02-001-999</t>
   </si>
   <si>
+    <t>RBMN</t>
+  </si>
+  <si>
+    <t>215-21-02-001-001-000</t>
+  </si>
+  <si>
+    <t>EXPERIENCIA</t>
+  </si>
+  <si>
     <t>BONIFICACION PROFESOR ENCARGADO ESC RURAL</t>
   </si>
   <si>
     <t>215-21-02-001-999-000</t>
   </si>
   <si>
-    <t>10035</t>
+    <t>ASIG PRIORITARIOS</t>
+  </si>
+  <si>
+    <t>10025</t>
+  </si>
+  <si>
+    <t>ASIG DE RESPONSABILIDAD</t>
+  </si>
+  <si>
+    <t>10027</t>
   </si>
   <si>
     <t>ASIG DE INCENTIVO PROFESIONAL</t>
   </si>
   <si>
+    <t>10039</t>
+  </si>
+  <si>
+    <t>DIFERENCIA AGUINALDO NAVIDAD</t>
+  </si>
+  <si>
     <t>10041</t>
   </si>
   <si>
-    <t>BRP TITULO</t>
-  </si>
-  <si>
-    <t>215-21-02-001-048</t>
-  </si>
-  <si>
     <t>10042</t>
   </si>
   <si>
     <t>BRP MENCION</t>
   </si>
   <si>
-    <t>10047</t>
+    <t>10045</t>
+  </si>
+  <si>
+    <t>DIFERENCIA BRP TITULO</t>
   </si>
   <si>
     <t>RETROACTIVO BRP TITULO</t>
@@ -386,6 +618,9 @@
     <t>RETROACTIVO ASIGNACION DE TRAMO</t>
   </si>
   <si>
+    <t>215-21-02-001-045</t>
+  </si>
+  <si>
     <t>10051</t>
   </si>
   <si>
@@ -398,16 +633,58 @@
     <t>DIFERENCIA ASIG. PRIORITARIO</t>
   </si>
   <si>
-    <t>215-21-02-005-003</t>
-  </si>
-  <si>
-    <t>10059</t>
-  </si>
-  <si>
-    <t>DIFERENCIA AGUINALDO DE NAVIDAD</t>
-  </si>
-  <si>
-    <t>215-21-02-005-001</t>
+    <t>10055</t>
+  </si>
+  <si>
+    <t>DIFERENCIA BRP</t>
+  </si>
+  <si>
+    <t>10056</t>
+  </si>
+  <si>
+    <t>DIFERENCIA MENCIÓN</t>
+  </si>
+  <si>
+    <t>10060</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE RBMN (ENERO)</t>
+  </si>
+  <si>
+    <t>10061</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE ASIG DE EXPERIENCIA (ENERO)</t>
+  </si>
+  <si>
+    <t>10062</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIGNACION DE RESPONSABILIDAD</t>
+  </si>
+  <si>
+    <t>10067</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE RBMN (DICIEMBRE)</t>
+  </si>
+  <si>
+    <t>10068</t>
+  </si>
+  <si>
+    <t>RETROACTIVO REAJUSTE ASIG EXPERIENCIA (DICIEMBRE)</t>
+  </si>
+  <si>
+    <t>10072</t>
+  </si>
+  <si>
+    <t>RETRO REAJUSTE ASIG INCENTIVO PROF (ENERO)</t>
+  </si>
+  <si>
+    <t>10073</t>
+  </si>
+  <si>
+    <t>RETRO REAJUSTE ASIG INCENTIVO PROF (DIC)</t>
   </si>
   <si>
     <t>10074</t>
@@ -419,10 +696,16 @@
     <t>215-21-02-001-004</t>
   </si>
   <si>
-    <t>215-21-02-001-001-000</t>
-  </si>
-  <si>
-    <t>215-21-02-001-044</t>
+    <t>10075</t>
+  </si>
+  <si>
+    <t>RETROACTIVO ASIG COMP ZONA (ENERO)</t>
+  </si>
+  <si>
+    <t>10077</t>
+  </si>
+  <si>
+    <t>RETRO REAJUSTE BONIF PROF ENCARGADO (ENERO)</t>
   </si>
   <si>
     <t>10081</t>
@@ -431,6 +714,12 @@
     <t>RETROACTIVO ASIGNACION DE EXPERIENCIA</t>
   </si>
   <si>
+    <t>10084</t>
+  </si>
+  <si>
+    <t>DIF DE SUELDO</t>
+  </si>
+  <si>
     <t>10085</t>
   </si>
   <si>
@@ -443,6 +732,12 @@
     <t>SNED DOCENTES</t>
   </si>
   <si>
+    <t>10089</t>
+  </si>
+  <si>
+    <t>RETROACTIVO RBMN</t>
+  </si>
+  <si>
     <t>R.B.M.N.</t>
   </si>
   <si>
@@ -455,9 +750,6 @@
     <t>215-21-02-001-002-000</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>215-21-02-001-048-000</t>
   </si>
   <si>
@@ -476,9 +768,6 @@
     <t>ASIG. TRAMO DESARROLLO PROFESIONAL</t>
   </si>
   <si>
-    <t>215-21-02-001-045</t>
-  </si>
-  <si>
     <t>215-21-02-001-045-000</t>
   </si>
   <si>
@@ -488,9 +777,6 @@
     <t>ALTA CONCENTRACION ALUMNOS PRIORITARIOS</t>
   </si>
   <si>
-    <t>215-21-02-001-046</t>
-  </si>
-  <si>
     <t>215-21-02-002-002</t>
   </si>
   <si>
@@ -500,13 +786,19 @@
     <t>PLANTA</t>
   </si>
   <si>
+    <t>215-21-01-001-019</t>
+  </si>
+  <si>
+    <t>215-21-01-001-049</t>
+  </si>
+  <si>
     <t>215-21-01-001-011</t>
   </si>
   <si>
     <t>215-21-01-001-011-000</t>
   </si>
   <si>
-    <t>215-21-01-001-019</t>
+    <t>215-21-01-001-050</t>
   </si>
   <si>
     <t>215-21-01-001-019-000</t>
@@ -518,43 +810,40 @@
     <t>215-21-01-001-999-000</t>
   </si>
   <si>
-    <t>215-21-01-001-049</t>
-  </si>
-  <si>
     <t>215-21-01-001-049-000</t>
   </si>
   <si>
-    <t>10015</t>
-  </si>
-  <si>
     <t>PLANILLA SUPLEMENTARIA LEY 20903</t>
   </si>
   <si>
-    <t>10040</t>
+    <t>215-21-01-001-047</t>
+  </si>
+  <si>
+    <t>215-21-01-001-048</t>
+  </si>
+  <si>
+    <t>ASIG RESPON ALTA CON ALUM PRIO</t>
+  </si>
+  <si>
+    <t>215-21-01-001-001-000</t>
+  </si>
+  <si>
+    <t>215-21-01-005-003</t>
   </si>
   <si>
     <t>ASIGNACION DE RESPONSABILIDAD ALTA CONC ALUM PRIOR</t>
   </si>
   <si>
-    <t>215-21-01-001-050</t>
-  </si>
-  <si>
-    <t>215-21-01-005-003</t>
-  </si>
-  <si>
-    <t>10062</t>
-  </si>
-  <si>
-    <t>RETROACTIVO ASIGNACION DE RESPONSABILIDAD</t>
+    <t>10046</t>
+  </si>
+  <si>
+    <t>DIFERENCIA BRP MENCION</t>
   </si>
   <si>
     <t>215-21-01-001-004</t>
   </si>
   <si>
-    <t>10077</t>
-  </si>
-  <si>
-    <t>RETRO REAJUSTE BONIF PROF ENCARGADO (ENERO)</t>
+    <t>215-21-01-001-051</t>
   </si>
   <si>
     <t>10088</t>
@@ -563,7 +852,13 @@
     <t>ADECO</t>
   </si>
   <si>
-    <t>215-21-01-001-001-000</t>
+    <t>215-21-01-003-002</t>
+  </si>
+  <si>
+    <t>10093</t>
+  </si>
+  <si>
+    <t>RETROACTIVO BONO ENCARGADO ESC RURAL</t>
   </si>
   <si>
     <t>215-21-01-001-050-000</t>
@@ -575,15 +870,9 @@
     <t>215-21-01-005-004</t>
   </si>
   <si>
-    <t>215-21-01-001-047</t>
-  </si>
-  <si>
     <t>215-21-01-001-047-000</t>
   </si>
   <si>
-    <t>215-21-01-001-048</t>
-  </si>
-  <si>
     <t>215-21-01-001-048-000</t>
   </si>
   <si>
@@ -596,6 +885,21 @@
     <t>SUPLENCIA</t>
   </si>
   <si>
+    <t>ASIGNACION DE TRAMO</t>
+  </si>
+  <si>
+    <t>ASIG DE RESPONSABILIDAD ALTA CONC ALUM PRIORITARIO</t>
+  </si>
+  <si>
+    <t>ASIG TRAMO</t>
+  </si>
+  <si>
+    <t>10043</t>
+  </si>
+  <si>
+    <t>10044</t>
+  </si>
+  <si>
     <t>HABER</t>
   </si>
   <si>
@@ -644,27 +948,21 @@
     <t>CHILENA CONSOLIDADA</t>
   </si>
   <si>
-    <t>10011</t>
-  </si>
-  <si>
     <t>MUTUAL DE SEGUROS</t>
   </si>
   <si>
+    <t>RETENCION JUDICIAL</t>
+  </si>
+  <si>
     <t>SECURITY PREVISION</t>
   </si>
   <si>
     <t>HOGAR DE CRISTO</t>
   </si>
   <si>
-    <t>10018</t>
-  </si>
-  <si>
     <t>AFAEC. ASOC. DE FUNC. NRO. 2 ASIST.</t>
   </si>
   <si>
-    <t>10019</t>
-  </si>
-  <si>
     <t>ASOC.GREMIAL NO DOCENTE</t>
   </si>
   <si>
@@ -674,30 +972,42 @@
     <t>REINTEGRO PRIORITARIO ENERO 2026</t>
   </si>
   <si>
-    <t>10023</t>
-  </si>
-  <si>
     <t>REINTEGRO ART 43 LEY 21109</t>
   </si>
   <si>
-    <t>10025</t>
+    <t>REINTEGRO ART 33 LEY 21724</t>
   </si>
   <si>
     <t>CONFEMUCH</t>
   </si>
   <si>
-    <t>10029</t>
+    <t>CONFEMUCH ENERO</t>
+  </si>
+  <si>
+    <t>REINTEGRO ASIG. EXPERIENCIA</t>
+  </si>
+  <si>
+    <t>DIFERENCIA DE SUELDO DE ENERO</t>
   </si>
   <si>
     <t>REINTEGRO ASIG EXPERIENCIA 21109</t>
   </si>
   <si>
-    <t>10030</t>
-  </si>
-  <si>
     <t>DIAS AUSENTISMO MES ANTERIOR</t>
   </si>
   <si>
+    <t>CREDITO CAJA LOS ANDES</t>
+  </si>
+  <si>
+    <t>SEGUROS CAJA LOS ANDES</t>
+  </si>
+  <si>
+    <t>REINTEGRO REMUNERACION</t>
+  </si>
+  <si>
+    <t>ASOCIACION NO DOCENTES LA LIGUA</t>
+  </si>
+  <si>
     <t>1004</t>
   </si>
   <si>
@@ -722,12 +1032,24 @@
     <t>RETENCION JUDICIAL 1</t>
   </si>
   <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>MONTO DIAS INASISTENCIAS</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
     <t>SEGURO CESANTIA</t>
   </si>
   <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>IMPUESTO UNICO RETROACTIVO</t>
+  </si>
+  <si>
     <t>500</t>
   </si>
   <si>
@@ -756,15 +1078,6 @@
   </si>
   <si>
     <t>4. La cuenta_presupuestaria_sugerida se precarga automáticamente cuando se detecta en archivos de referencia.</t>
-  </si>
-  <si>
-    <t>215-21-01-001-051</t>
-  </si>
-  <si>
-    <t>215-21-02-001-049</t>
-  </si>
-  <si>
-    <t>215-21-01-003-002</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1118,7 +1431,7 @@
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
@@ -1232,10 +1545,7 @@
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -1255,10 +1565,10 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -1267,12 +1577,12 @@
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1287,13 +1597,13 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1310,10 +1620,10 @@
         <v>13</v>
       </c>
       <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
         <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -1322,7 +1632,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1339,19 +1649,16 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1368,19 +1675,16 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1397,24 +1701,21 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1426,16 +1727,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" t="s">
-        <v>154</v>
-      </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1452,16 +1753,19 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1478,16 +1782,16 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
         <v>41</v>
       </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1504,16 +1808,16 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
         <v>43</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>44</v>
       </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1536,7 +1840,7 @@
         <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
@@ -1562,7 +1866,10 @@
         <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1588,7 +1895,7 @@
         <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
         <v>50</v>
@@ -1614,7 +1921,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
         <v>52</v>
@@ -1640,7 +1947,7 @@
         <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
         <v>54</v>
@@ -1648,7 +1955,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
@@ -1666,7 +1973,7 @@
         <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
         <v>56</v>
@@ -1718,7 +2025,7 @@
         <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
         <v>60</v>
@@ -1726,7 +2033,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1744,7 +2051,7 @@
         <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
         <v>62</v>
@@ -1770,10 +2077,7 @@
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
         <v>64</v>
@@ -1793,16 +2097,16 @@
         <v>13</v>
       </c>
       <c r="E25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" t="s">
         <v>66</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1819,16 +2123,19 @@
         <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
       <c r="I26" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -1845,10 +2152,10 @@
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G27" t="s">
         <v>17</v>
@@ -1857,7 +2164,7 @@
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -1874,19 +2181,16 @@
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
         <v>17</v>
       </c>
-      <c r="H28" t="s">
-        <v>17</v>
-      </c>
       <c r="I28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -1903,24 +2207,21 @@
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -1932,19 +2233,16 @@
         <v>13</v>
       </c>
       <c r="E30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" t="s">
         <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>77</v>
       </c>
       <c r="G30" t="s">
         <v>17</v>
       </c>
-      <c r="H30" t="s">
-        <v>17</v>
-      </c>
       <c r="I30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -1961,19 +2259,16 @@
         <v>13</v>
       </c>
       <c r="E31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s">
         <v>78</v>
       </c>
-      <c r="F31" t="s">
-        <v>79</v>
-      </c>
       <c r="G31" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -1987,19 +2282,19 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I32" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -2013,19 +2308,19 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
         <v>80</v>
       </c>
-      <c r="E33" t="s">
-        <v>18</v>
-      </c>
       <c r="F33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -2039,19 +2334,19 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -2065,19 +2360,19 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -2091,19 +2386,19 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
         <v>86</v>
       </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -2117,19 +2412,19 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -2143,19 +2438,19 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I38" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -2169,19 +2464,19 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -2195,19 +2490,19 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -2221,19 +2516,19 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -2247,19 +2542,19 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I42" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2273,19 +2568,19 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I43" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -2299,19 +2594,19 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="G44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2325,19 +2620,19 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2351,19 +2646,19 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I46" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -2377,19 +2672,19 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -2403,19 +2698,19 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="G48" t="s">
         <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -2429,19 +2724,19 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="G49" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -2455,22 +2750,19 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F50" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>99</v>
-      </c>
-      <c r="H50" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -2484,22 +2776,22 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="H51" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="I51" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -2513,19 +2805,19 @@
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="F52" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G52" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="I52" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2539,22 +2831,19 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
-      </c>
-      <c r="H53" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -2568,22 +2857,19 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="G54" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2597,19 +2883,22 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G55" t="s">
-        <v>111</v>
+        <v>17</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2623,24 +2912,27 @@
         <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G56" t="s">
-        <v>111</v>
+        <v>17</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
@@ -2649,24 +2941,27 @@
         <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G57" t="s">
-        <v>111</v>
+        <v>17</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
@@ -2675,24 +2970,24 @@
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F58" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
@@ -2701,24 +2996,27 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G59" t="s">
-        <v>150</v>
+        <v>17</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
@@ -2727,24 +3025,27 @@
         <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>17</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
@@ -2753,24 +3054,24 @@
         <v>12</v>
       </c>
       <c r="D61" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="F61" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G61" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
@@ -2779,19 +3080,19 @@
         <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E62" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -2805,19 +3106,19 @@
         <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F63" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="G63" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I63" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -2831,19 +3132,19 @@
         <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -2857,24 +3158,24 @@
         <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="G65" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
@@ -2883,19 +3184,19 @@
         <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E66" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="F66" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G66" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -2909,19 +3210,19 @@
         <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E67" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G67" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2935,19 +3236,19 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="F68" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G68" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -2961,19 +3262,19 @@
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E69" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2987,19 +3288,19 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E70" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="F70" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G70" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
@@ -3013,24 +3314,24 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E71" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="G71" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -3039,24 +3340,24 @@
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E72" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G72" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I72" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -3065,19 +3366,19 @@
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E73" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="F73" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -3091,22 +3392,19 @@
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E74" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G74" t="s">
-        <v>131</v>
-      </c>
-      <c r="H74" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -3120,22 +3418,19 @@
         <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E75" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F75" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="G75" t="s">
-        <v>142</v>
-      </c>
-      <c r="H75" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -3149,22 +3444,19 @@
         <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E76" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="F76" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="G76" t="s">
-        <v>111</v>
-      </c>
-      <c r="H76" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -3178,22 +3470,19 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E77" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="F77" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s">
-        <v>111</v>
-      </c>
-      <c r="H77" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -3207,19 +3496,19 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E78" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F78" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="G78" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -3233,19 +3522,19 @@
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="F79" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="G79" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -3259,22 +3548,19 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E80" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="G80" t="s">
-        <v>150</v>
-      </c>
-      <c r="H80" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -3288,22 +3574,19 @@
         <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E81" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F81" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G81" t="s">
-        <v>154</v>
-      </c>
-      <c r="H81" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -3317,22 +3600,19 @@
         <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E82" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="G82" t="s">
-        <v>155</v>
-      </c>
-      <c r="H82" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -3346,22 +3626,19 @@
         <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E83" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="F83" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="G83" t="s">
-        <v>155</v>
-      </c>
-      <c r="H83" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -3375,22 +3652,19 @@
         <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E84" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="F84" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="G84" t="s">
-        <v>155</v>
-      </c>
-      <c r="H84" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -3404,22 +3678,19 @@
         <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E85" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="F85" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="G85" t="s">
-        <v>155</v>
-      </c>
-      <c r="H85" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="I85" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -3433,19 +3704,19 @@
         <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="F86" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="G86" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
@@ -3459,22 +3730,19 @@
         <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="F87" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="G87" t="s">
-        <v>158</v>
-      </c>
-      <c r="H87" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
@@ -3488,22 +3756,19 @@
         <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E88" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F88" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="G88" t="s">
-        <v>160</v>
-      </c>
-      <c r="H88" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
@@ -3517,22 +3782,19 @@
         <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E89" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="G89" t="s">
-        <v>162</v>
-      </c>
-      <c r="H89" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
@@ -3546,22 +3808,19 @@
         <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E90" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="F90" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="G90" t="s">
-        <v>164</v>
-      </c>
-      <c r="H90" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
@@ -3575,22 +3834,19 @@
         <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E91" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="F91" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="G91" t="s">
-        <v>160</v>
-      </c>
-      <c r="H91" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
@@ -3604,22 +3860,19 @@
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E92" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="F92" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="G92" t="s">
-        <v>162</v>
-      </c>
-      <c r="H92" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -3633,22 +3886,19 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E93" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="F93" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>162</v>
-      </c>
-      <c r="H93" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="I93" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
@@ -3662,22 +3912,19 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="G94" t="s">
-        <v>162</v>
-      </c>
-      <c r="H94" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="I94" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
@@ -3691,22 +3938,19 @@
         <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E95" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="F95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G95" t="s">
-        <v>160</v>
-      </c>
-      <c r="H95" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="I95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -3720,19 +3964,19 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="F96" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G96" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="I96" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
@@ -3746,24 +3990,27 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E97" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="G97" t="s">
-        <v>170</v>
+        <v>23</v>
+      </c>
+      <c r="H97" t="s">
+        <v>168</v>
       </c>
       <c r="I97" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
@@ -3772,24 +4019,24 @@
         <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E98" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F98" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G98" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I98" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -3798,24 +4045,27 @@
         <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="G99" t="s">
-        <v>170</v>
+        <v>23</v>
+      </c>
+      <c r="H99" t="s">
+        <v>169</v>
       </c>
       <c r="I99" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B100" t="s">
         <v>11</v>
@@ -3824,24 +4074,24 @@
         <v>12</v>
       </c>
       <c r="D100" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E100" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="F100" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="G100" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I100" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="B101" t="s">
         <v>11</v>
@@ -3850,24 +4100,24 @@
         <v>12</v>
       </c>
       <c r="D101" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G101" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="I101" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B102" t="s">
         <v>11</v>
@@ -3876,24 +4126,24 @@
         <v>12</v>
       </c>
       <c r="D102" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E102" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="F102" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="G102" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I102" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B103" t="s">
         <v>11</v>
@@ -3902,19 +4152,19 @@
         <v>12</v>
       </c>
       <c r="D103" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="F103" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="G103" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="I103" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3928,19 +4178,22 @@
         <v>12</v>
       </c>
       <c r="D104" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="F104" t="s">
-        <v>46</v>
+        <v>174</v>
       </c>
       <c r="G104" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="H104" t="s">
+        <v>175</v>
       </c>
       <c r="I104" t="s">
-        <v>46</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
@@ -3954,24 +4207,24 @@
         <v>12</v>
       </c>
       <c r="D105" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E105" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="F105" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G105" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="I105" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
         <v>11</v>
@@ -3980,19 +4233,19 @@
         <v>12</v>
       </c>
       <c r="D106" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E106" t="s">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="F106" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G106" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I106" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -4006,24 +4259,24 @@
         <v>12</v>
       </c>
       <c r="D107" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E107" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="F107" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G107" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="I107" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
         <v>11</v>
@@ -4032,24 +4285,24 @@
         <v>12</v>
       </c>
       <c r="D108" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E108" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="F108" t="s">
-        <v>176</v>
+        <v>50</v>
       </c>
       <c r="G108" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>176</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B109" t="s">
         <v>11</v>
@@ -4058,24 +4311,24 @@
         <v>12</v>
       </c>
       <c r="D109" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="G109" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I109" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B110" t="s">
         <v>11</v>
@@ -4084,24 +4337,24 @@
         <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E110" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F110" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G110" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="I110" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B111" t="s">
         <v>11</v>
@@ -4110,19 +4363,22 @@
         <v>12</v>
       </c>
       <c r="D111" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E111" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="F111" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="G111" t="s">
-        <v>183</v>
+        <v>170</v>
+      </c>
+      <c r="H111" t="s">
+        <v>175</v>
       </c>
       <c r="I111" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
@@ -4136,24 +4392,24 @@
         <v>12</v>
       </c>
       <c r="D112" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F112" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="G112" t="s">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="I112" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B113" t="s">
         <v>11</v>
@@ -4162,24 +4418,24 @@
         <v>12</v>
       </c>
       <c r="D113" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E113" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F113" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="G113" t="s">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="I113" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B114" t="s">
         <v>11</v>
@@ -4188,19 +4444,19 @@
         <v>12</v>
       </c>
       <c r="D114" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E114" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F114" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G114" t="s">
-        <v>246</v>
+        <v>87</v>
       </c>
       <c r="I114" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
@@ -4214,22 +4470,19 @@
         <v>12</v>
       </c>
       <c r="D115" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E115" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="G115" t="s">
-        <v>179</v>
-      </c>
-      <c r="H115" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I115" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -4243,22 +4496,19 @@
         <v>12</v>
       </c>
       <c r="D116" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E116" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="F116" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="G116" t="s">
-        <v>179</v>
-      </c>
-      <c r="H116" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="I116" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -4272,22 +4522,19 @@
         <v>12</v>
       </c>
       <c r="D117" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E117" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="F117" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="G117" t="s">
-        <v>180</v>
-      </c>
-      <c r="H117" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="I117" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
@@ -4301,22 +4548,19 @@
         <v>12</v>
       </c>
       <c r="D118" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E118" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="F118" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="G118" t="s">
-        <v>180</v>
-      </c>
-      <c r="H118" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="I118" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4330,19 +4574,19 @@
         <v>12</v>
       </c>
       <c r="D119" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E119" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="F119" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="G119" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="I119" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
@@ -4356,19 +4600,19 @@
         <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="F120" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="G120" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="I120" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
@@ -4382,22 +4626,19 @@
         <v>12</v>
       </c>
       <c r="D121" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E121" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F121" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="G121" t="s">
-        <v>183</v>
-      </c>
-      <c r="H121" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
@@ -4411,22 +4652,19 @@
         <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E122" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="F122" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="G122" t="s">
-        <v>185</v>
-      </c>
-      <c r="H122" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I122" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4440,22 +4678,19 @@
         <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E123" t="s">
-        <v>70</v>
+        <v>196</v>
       </c>
       <c r="F123" t="s">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="G123" t="s">
-        <v>187</v>
-      </c>
-      <c r="H123" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="I123" t="s">
-        <v>71</v>
+        <v>197</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
@@ -4469,22 +4704,19 @@
         <v>12</v>
       </c>
       <c r="D124" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E124" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="F124" t="s">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="G124" t="s">
-        <v>187</v>
-      </c>
-      <c r="H124" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="I124" t="s">
-        <v>75</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
@@ -4498,22 +4730,19 @@
         <v>12</v>
       </c>
       <c r="D125" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E125" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="F125" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="G125" t="s">
-        <v>187</v>
-      </c>
-      <c r="H125" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="I125" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
@@ -4527,22 +4756,19 @@
         <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E126" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F126" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G126" t="s">
-        <v>187</v>
-      </c>
-      <c r="H126" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="I126" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
@@ -4556,19 +4782,19 @@
         <v>12</v>
       </c>
       <c r="D127" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E127" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F127" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G127" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -4582,24 +4808,24 @@
         <v>12</v>
       </c>
       <c r="D128" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E128" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F128" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G128" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="I128" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B129" t="s">
         <v>11</v>
@@ -4608,24 +4834,24 @@
         <v>12</v>
       </c>
       <c r="D129" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E129" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="F129" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="G129" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I129" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B130" t="s">
         <v>11</v>
@@ -4634,24 +4860,24 @@
         <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E130" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="F130" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="G130" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I130" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B131" t="s">
         <v>11</v>
@@ -4660,24 +4886,24 @@
         <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E131" t="s">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="F131" t="s">
-        <v>38</v>
+        <v>207</v>
       </c>
       <c r="G131" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I131" t="s">
-        <v>38</v>
+        <v>207</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B132" t="s">
         <v>11</v>
@@ -4686,19 +4912,19 @@
         <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E132" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="F132" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="G132" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I132" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -4712,24 +4938,24 @@
         <v>12</v>
       </c>
       <c r="D133" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E133" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="F133" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="G133" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I133" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B134" t="s">
         <v>11</v>
@@ -4738,19 +4964,19 @@
         <v>12</v>
       </c>
       <c r="D134" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E134" t="s">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F134" t="s">
-        <v>54</v>
+        <v>211</v>
       </c>
       <c r="G134" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I134" t="s">
-        <v>54</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -4764,24 +4990,24 @@
         <v>12</v>
       </c>
       <c r="D135" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E135" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F135" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="G135" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I135" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s">
         <v>11</v>
@@ -4790,24 +5016,24 @@
         <v>12</v>
       </c>
       <c r="D136" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E136" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="F136" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="G136" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I136" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B137" t="s">
         <v>11</v>
@@ -4816,19 +5042,19 @@
         <v>12</v>
       </c>
       <c r="D137" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E137" t="s">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="F137" t="s">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="G137" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I137" t="s">
-        <v>138</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
@@ -4842,22 +5068,19 @@
         <v>12</v>
       </c>
       <c r="D138" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E138" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="F138" t="s">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="G138" t="s">
-        <v>16</v>
-      </c>
-      <c r="H138" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I138" t="s">
-        <v>139</v>
+        <v>215</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4871,22 +5094,19 @@
         <v>12</v>
       </c>
       <c r="D139" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="F139" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="G139" t="s">
-        <v>16</v>
-      </c>
-      <c r="H139" t="s">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="I139" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
@@ -4900,22 +5120,19 @@
         <v>12</v>
       </c>
       <c r="D140" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E140" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="F140" t="s">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="G140" t="s">
-        <v>16</v>
-      </c>
-      <c r="H140" t="s">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="I140" t="s">
-        <v>110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
@@ -4929,22 +5146,19 @@
         <v>12</v>
       </c>
       <c r="D141" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E141" t="s">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="F141" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="G141" t="s">
-        <v>16</v>
-      </c>
-      <c r="H141" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I141" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -4958,19 +5172,19 @@
         <v>12</v>
       </c>
       <c r="D142" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E142" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F142" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="G142" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I142" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
@@ -4984,19 +5198,19 @@
         <v>12</v>
       </c>
       <c r="D143" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E143" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F143" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="G143" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I143" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
@@ -5010,22 +5224,19 @@
         <v>12</v>
       </c>
       <c r="D144" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E144" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="F144" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="G144" t="s">
-        <v>16</v>
-      </c>
-      <c r="H144" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I144" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
@@ -5039,22 +5250,19 @@
         <v>12</v>
       </c>
       <c r="D145" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E145" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="F145" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="G145" t="s">
-        <v>16</v>
-      </c>
-      <c r="H145" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="I145" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -5068,22 +5276,19 @@
         <v>12</v>
       </c>
       <c r="D146" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E146" t="s">
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="F146" t="s">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="G146" t="s">
-        <v>16</v>
-      </c>
-      <c r="H146" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I146" t="s">
-        <v>71</v>
+        <v>226</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
@@ -5097,22 +5302,19 @@
         <v>12</v>
       </c>
       <c r="D147" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E147" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="F147" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="G147" t="s">
-        <v>16</v>
-      </c>
-      <c r="H147" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I147" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -5126,22 +5328,19 @@
         <v>12</v>
       </c>
       <c r="D148" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E148" t="s">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="F148" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="G148" t="s">
-        <v>16</v>
-      </c>
-      <c r="H148" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="I148" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
@@ -5155,22 +5354,19 @@
         <v>12</v>
       </c>
       <c r="D149" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E149" t="s">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="F149" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="G149" t="s">
-        <v>16</v>
-      </c>
-      <c r="H149" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I149" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
@@ -5178,22 +5374,28 @@
         <v>10</v>
       </c>
       <c r="B150" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D150" t="s">
+        <v>166</v>
       </c>
       <c r="E150" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="F150" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="G150" t="s">
-        <v>192</v>
+        <v>172</v>
+      </c>
+      <c r="H150" t="s">
+        <v>172</v>
       </c>
       <c r="I150" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -5201,22 +5403,28 @@
         <v>10</v>
       </c>
       <c r="B151" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D151" t="s">
+        <v>166</v>
       </c>
       <c r="E151" t="s">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="F151" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="G151" t="s">
-        <v>192</v>
+        <v>236</v>
+      </c>
+      <c r="H151" t="s">
+        <v>172</v>
       </c>
       <c r="I151" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -5224,22 +5432,28 @@
         <v>10</v>
       </c>
       <c r="B152" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D152" t="s">
+        <v>166</v>
       </c>
       <c r="E152" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="F152" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G152" t="s">
-        <v>192</v>
+        <v>121</v>
+      </c>
+      <c r="H152" t="s">
+        <v>237</v>
       </c>
       <c r="I152" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
@@ -5247,22 +5461,28 @@
         <v>10</v>
       </c>
       <c r="B153" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D153" t="s">
+        <v>166</v>
       </c>
       <c r="E153" t="s">
-        <v>95</v>
+        <v>238</v>
       </c>
       <c r="F153" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="G153" t="s">
-        <v>192</v>
+        <v>121</v>
+      </c>
+      <c r="H153" t="s">
+        <v>237</v>
       </c>
       <c r="I153" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
@@ -5270,22 +5490,25 @@
         <v>10</v>
       </c>
       <c r="B154" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C154" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D154" t="s">
+        <v>166</v>
       </c>
       <c r="E154" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="F154" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="G154" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="I154" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
@@ -5293,22 +5516,25 @@
         <v>10</v>
       </c>
       <c r="B155" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D155" t="s">
+        <v>166</v>
       </c>
       <c r="E155" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="F155" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="G155" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="I155" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -5316,22 +5542,28 @@
         <v>10</v>
       </c>
       <c r="B156" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="D156" t="s">
+        <v>166</v>
       </c>
       <c r="E156" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="F156" t="s">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="G156" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="H156" t="s">
+        <v>243</v>
       </c>
       <c r="I156" t="s">
-        <v>79</v>
+        <v>242</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
@@ -5339,22 +5571,28 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D157" t="s">
+        <v>166</v>
       </c>
       <c r="E157" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="F157" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="G157" t="s">
-        <v>192</v>
+        <v>34</v>
+      </c>
+      <c r="H157" t="s">
+        <v>237</v>
       </c>
       <c r="I157" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
@@ -5362,22 +5600,28 @@
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D158" t="s">
+        <v>166</v>
       </c>
       <c r="E158" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="F158" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="G158" t="s">
-        <v>192</v>
+        <v>246</v>
+      </c>
+      <c r="H158" t="s">
+        <v>247</v>
       </c>
       <c r="I158" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
@@ -5385,22 +5629,28 @@
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D159" t="s">
+        <v>166</v>
       </c>
       <c r="E159" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="F159" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="G159" t="s">
-        <v>192</v>
+        <v>246</v>
+      </c>
+      <c r="H159" t="s">
+        <v>247</v>
       </c>
       <c r="I159" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -5408,22 +5658,25 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D160" t="s">
+        <v>166</v>
       </c>
       <c r="E160" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="F160" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="G160" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="I160" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
@@ -5431,22 +5684,28 @@
         <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D161" t="s">
+        <v>166</v>
       </c>
       <c r="E161" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F161" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="G161" t="s">
-        <v>192</v>
+        <v>246</v>
+      </c>
+      <c r="H161" t="s">
+        <v>247</v>
       </c>
       <c r="I161" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
@@ -5454,22 +5713,28 @@
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D162" t="s">
+        <v>166</v>
       </c>
       <c r="E162" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F162" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="G162" t="s">
-        <v>192</v>
+        <v>246</v>
+      </c>
+      <c r="H162" t="s">
+        <v>247</v>
       </c>
       <c r="I162" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
@@ -5477,22 +5742,25 @@
         <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D163" t="s">
+        <v>248</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F163" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="G163" t="s">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="I163" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -5500,22 +5768,25 @@
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
+        <v>248</v>
       </c>
       <c r="E164" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="G164" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="I164" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -5523,22 +5794,25 @@
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D165" t="s">
+        <v>248</v>
       </c>
       <c r="E165" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="F165" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="G165" t="s">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="I165" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -5546,22 +5820,28 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D166" t="s">
+        <v>248</v>
       </c>
       <c r="E166" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F166" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>192</v>
+        <v>251</v>
+      </c>
+      <c r="H166" t="s">
+        <v>252</v>
       </c>
       <c r="I166" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -5569,22 +5849,25 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D167" t="s">
+        <v>248</v>
       </c>
       <c r="E167" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="F167" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="G167" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="I167" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -5592,22 +5875,28 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D168" t="s">
+        <v>248</v>
       </c>
       <c r="E168" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="F168" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="G168" t="s">
-        <v>192</v>
+        <v>249</v>
+      </c>
+      <c r="H168" t="s">
+        <v>254</v>
       </c>
       <c r="I168" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -5615,45 +5904,57 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D169" t="s">
+        <v>248</v>
       </c>
       <c r="E169" t="s">
+        <v>27</v>
+      </c>
+      <c r="F169" t="s">
         <v>28</v>
       </c>
-      <c r="F169" t="s">
-        <v>208</v>
-      </c>
       <c r="G169" t="s">
-        <v>192</v>
+        <v>255</v>
+      </c>
+      <c r="H169" t="s">
+        <v>256</v>
       </c>
       <c r="I169" t="s">
-        <v>208</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D170" t="s">
+        <v>248</v>
       </c>
       <c r="E170" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="F170" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="G170" t="s">
-        <v>192</v>
+        <v>250</v>
+      </c>
+      <c r="H170" t="s">
+        <v>257</v>
       </c>
       <c r="I170" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
@@ -5661,22 +5962,28 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D171" t="s">
+        <v>248</v>
       </c>
       <c r="E171" t="s">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="F171" t="s">
-        <v>211</v>
+        <v>39</v>
       </c>
       <c r="G171" t="s">
-        <v>192</v>
+        <v>249</v>
+      </c>
+      <c r="H171" t="s">
+        <v>254</v>
       </c>
       <c r="I171" t="s">
-        <v>211</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -5684,22 +5991,28 @@
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D172" t="s">
+        <v>248</v>
       </c>
       <c r="E172" t="s">
-        <v>212</v>
+        <v>151</v>
       </c>
       <c r="F172" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="G172" t="s">
-        <v>192</v>
+        <v>255</v>
+      </c>
+      <c r="H172" t="s">
+        <v>256</v>
       </c>
       <c r="I172" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -5707,22 +6020,25 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D173" t="s">
+        <v>248</v>
       </c>
       <c r="E173" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F173" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="G173" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="I173" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -5730,22 +6046,28 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D174" t="s">
+        <v>248</v>
       </c>
       <c r="E174" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="F174" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="G174" t="s">
-        <v>192</v>
+        <v>255</v>
+      </c>
+      <c r="H174" t="s">
+        <v>256</v>
       </c>
       <c r="I174" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -5753,22 +6075,25 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D175" t="s">
+        <v>248</v>
       </c>
       <c r="E175" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="F175" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G175" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="I175" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -5776,22 +6101,25 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D176" t="s">
+        <v>248</v>
       </c>
       <c r="E176" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="F176" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="G176" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="I176" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
@@ -5799,45 +6127,54 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D177" t="s">
+        <v>248</v>
       </c>
       <c r="E177" t="s">
-        <v>220</v>
+        <v>63</v>
       </c>
       <c r="F177" t="s">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="G177" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="I177" t="s">
-        <v>221</v>
+        <v>64</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D178" t="s">
+        <v>248</v>
       </c>
       <c r="E178" t="s">
-        <v>222</v>
+        <v>65</v>
       </c>
       <c r="F178" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="G178" t="s">
-        <v>192</v>
+        <v>255</v>
+      </c>
+      <c r="H178" t="s">
+        <v>256</v>
       </c>
       <c r="I178" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -5845,22 +6182,25 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D179" t="s">
+        <v>248</v>
       </c>
       <c r="E179" t="s">
-        <v>224</v>
+        <v>68</v>
       </c>
       <c r="F179" t="s">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="G179" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="I179" t="s">
-        <v>225</v>
+        <v>105</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -5868,22 +6208,25 @@
         <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D180" t="s">
+        <v>248</v>
       </c>
       <c r="E180" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="F180" t="s">
-        <v>227</v>
+        <v>71</v>
       </c>
       <c r="G180" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="I180" t="s">
-        <v>227</v>
+        <v>71</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
@@ -5891,22 +6234,28 @@
         <v>10</v>
       </c>
       <c r="B181" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D181" t="s">
+        <v>248</v>
       </c>
       <c r="E181" t="s">
-        <v>228</v>
+        <v>72</v>
       </c>
       <c r="F181" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="G181" t="s">
-        <v>192</v>
+        <v>249</v>
+      </c>
+      <c r="H181" t="s">
+        <v>254</v>
       </c>
       <c r="I181" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
@@ -5914,22 +6263,25 @@
         <v>10</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D182" t="s">
+        <v>248</v>
       </c>
       <c r="E182" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="F182" t="s">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="G182" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="I182" t="s">
-        <v>231</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -5937,22 +6289,25 @@
         <v>10</v>
       </c>
       <c r="B183" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D183" t="s">
+        <v>248</v>
       </c>
       <c r="E183" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="F183" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="G183" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="I183" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
@@ -5960,22 +6315,25 @@
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>193</v>
+        <v>12</v>
+      </c>
+      <c r="D184" t="s">
+        <v>248</v>
       </c>
       <c r="E184" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="F184" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="G184" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="I184" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
@@ -5983,26 +6341,3666 @@
         <v>10</v>
       </c>
       <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" t="s">
+        <v>248</v>
+      </c>
+      <c r="E185" t="s">
+        <v>265</v>
+      </c>
+      <c r="F185" t="s">
+        <v>266</v>
+      </c>
+      <c r="G185" t="s">
+        <v>253</v>
+      </c>
+      <c r="I185" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>10</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" t="s">
+        <v>248</v>
+      </c>
+      <c r="E186" t="s">
+        <v>75</v>
+      </c>
+      <c r="F186" t="s">
+        <v>188</v>
+      </c>
+      <c r="G186" t="s">
+        <v>253</v>
+      </c>
+      <c r="I186" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>12</v>
+      </c>
+      <c r="D187" t="s">
+        <v>248</v>
+      </c>
+      <c r="E187" t="s">
+        <v>189</v>
+      </c>
+      <c r="F187" t="s">
         <v>190</v>
       </c>
-      <c r="C185" t="s">
-        <v>236</v>
-      </c>
-      <c r="E185" t="s">
-        <v>237</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="G187" t="s">
+        <v>253</v>
+      </c>
+      <c r="I187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>10</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188" t="s">
+        <v>248</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+      <c r="F188" t="s">
+        <v>192</v>
+      </c>
+      <c r="G188" t="s">
+        <v>259</v>
+      </c>
+      <c r="I188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>10</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" t="s">
+        <v>248</v>
+      </c>
+      <c r="E189" t="s">
+        <v>77</v>
+      </c>
+      <c r="F189" t="s">
+        <v>78</v>
+      </c>
+      <c r="G189" t="s">
+        <v>260</v>
+      </c>
+      <c r="I189" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>10</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" t="s">
+        <v>248</v>
+      </c>
+      <c r="E190" t="s">
+        <v>194</v>
+      </c>
+      <c r="F190" t="s">
+        <v>195</v>
+      </c>
+      <c r="G190" t="s">
+        <v>259</v>
+      </c>
+      <c r="I190" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>10</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" t="s">
+        <v>248</v>
+      </c>
+      <c r="E191" t="s">
+        <v>196</v>
+      </c>
+      <c r="F191" t="s">
+        <v>197</v>
+      </c>
+      <c r="G191" t="s">
+        <v>260</v>
+      </c>
+      <c r="I191" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>10</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" t="s">
+        <v>248</v>
+      </c>
+      <c r="E192" t="s">
+        <v>82</v>
+      </c>
+      <c r="F192" t="s">
+        <v>50</v>
+      </c>
+      <c r="G192" t="s">
+        <v>263</v>
+      </c>
+      <c r="I192" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>10</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" t="s">
+        <v>248</v>
+      </c>
+      <c r="E193" t="s">
+        <v>83</v>
+      </c>
+      <c r="F193" t="s">
+        <v>84</v>
+      </c>
+      <c r="G193" t="s">
+        <v>263</v>
+      </c>
+      <c r="I193" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>12</v>
+      </c>
+      <c r="D194" t="s">
+        <v>248</v>
+      </c>
+      <c r="E194" t="s">
+        <v>85</v>
+      </c>
+      <c r="F194" t="s">
+        <v>86</v>
+      </c>
+      <c r="G194" t="s">
+        <v>263</v>
+      </c>
+      <c r="I194" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>12</v>
+      </c>
+      <c r="D195" t="s">
+        <v>248</v>
+      </c>
+      <c r="E195" t="s">
+        <v>202</v>
+      </c>
+      <c r="F195" t="s">
+        <v>203</v>
+      </c>
+      <c r="G195" t="s">
+        <v>262</v>
+      </c>
+      <c r="I195" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>10</v>
+      </c>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>12</v>
+      </c>
+      <c r="D196" t="s">
+        <v>248</v>
+      </c>
+      <c r="E196" t="s">
+        <v>204</v>
+      </c>
+      <c r="F196" t="s">
+        <v>205</v>
+      </c>
+      <c r="G196" t="s">
+        <v>259</v>
+      </c>
+      <c r="I196" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" t="s">
+        <v>248</v>
+      </c>
+      <c r="E197" t="s">
+        <v>206</v>
+      </c>
+      <c r="F197" t="s">
+        <v>207</v>
+      </c>
+      <c r="G197" t="s">
+        <v>249</v>
+      </c>
+      <c r="I197" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>10</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>12</v>
+      </c>
+      <c r="D198" t="s">
+        <v>248</v>
+      </c>
+      <c r="E198" t="s">
+        <v>92</v>
+      </c>
+      <c r="F198" t="s">
+        <v>93</v>
+      </c>
+      <c r="G198" t="s">
+        <v>262</v>
+      </c>
+      <c r="I198" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>10</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>12</v>
+      </c>
+      <c r="D199" t="s">
+        <v>248</v>
+      </c>
+      <c r="E199" t="s">
+        <v>208</v>
+      </c>
+      <c r="F199" t="s">
+        <v>209</v>
+      </c>
+      <c r="G199" t="s">
+        <v>262</v>
+      </c>
+      <c r="I199" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>10</v>
+      </c>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>12</v>
+      </c>
+      <c r="D200" t="s">
+        <v>248</v>
+      </c>
+      <c r="E200" t="s">
+        <v>210</v>
+      </c>
+      <c r="F200" t="s">
+        <v>211</v>
+      </c>
+      <c r="G200" t="s">
+        <v>259</v>
+      </c>
+      <c r="I200" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>10</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" t="s">
+        <v>248</v>
+      </c>
+      <c r="E201" t="s">
+        <v>98</v>
+      </c>
+      <c r="F201" t="s">
+        <v>99</v>
+      </c>
+      <c r="G201" t="s">
+        <v>249</v>
+      </c>
+      <c r="I201" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>10</v>
+      </c>
+      <c r="B202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" t="s">
+        <v>248</v>
+      </c>
+      <c r="E202" t="s">
+        <v>100</v>
+      </c>
+      <c r="F202" t="s">
+        <v>101</v>
+      </c>
+      <c r="G202" t="s">
+        <v>249</v>
+      </c>
+      <c r="I202" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>10</v>
+      </c>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" t="s">
+        <v>12</v>
+      </c>
+      <c r="D203" t="s">
+        <v>248</v>
+      </c>
+      <c r="E203" t="s">
+        <v>212</v>
+      </c>
+      <c r="F203" t="s">
+        <v>213</v>
+      </c>
+      <c r="G203" t="s">
+        <v>255</v>
+      </c>
+      <c r="I203" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>12</v>
+      </c>
+      <c r="D204" t="s">
+        <v>248</v>
+      </c>
+      <c r="E204" t="s">
+        <v>214</v>
+      </c>
+      <c r="F204" t="s">
+        <v>215</v>
+      </c>
+      <c r="G204" t="s">
+        <v>255</v>
+      </c>
+      <c r="I204" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>10</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>248</v>
+      </c>
+      <c r="E205" t="s">
+        <v>216</v>
+      </c>
+      <c r="F205" t="s">
+        <v>217</v>
+      </c>
+      <c r="G205" t="s">
+        <v>267</v>
+      </c>
+      <c r="I205" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>10</v>
+      </c>
+      <c r="B206" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" t="s">
+        <v>248</v>
+      </c>
+      <c r="E206" t="s">
+        <v>219</v>
+      </c>
+      <c r="F206" t="s">
+        <v>220</v>
+      </c>
+      <c r="G206" t="s">
+        <v>267</v>
+      </c>
+      <c r="I206" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>10</v>
+      </c>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" t="s">
+        <v>12</v>
+      </c>
+      <c r="D207" t="s">
+        <v>248</v>
+      </c>
+      <c r="E207" t="s">
+        <v>102</v>
+      </c>
+      <c r="F207" t="s">
+        <v>103</v>
+      </c>
+      <c r="G207" t="s">
+        <v>251</v>
+      </c>
+      <c r="I207" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>10</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" t="s">
+        <v>12</v>
+      </c>
+      <c r="D208" t="s">
+        <v>248</v>
+      </c>
+      <c r="E208" t="s">
+        <v>221</v>
+      </c>
+      <c r="F208" t="s">
+        <v>222</v>
+      </c>
+      <c r="G208" t="s">
+        <v>255</v>
+      </c>
+      <c r="I208" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>10</v>
+      </c>
+      <c r="B209" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" t="s">
+        <v>248</v>
+      </c>
+      <c r="E209" t="s">
+        <v>104</v>
+      </c>
+      <c r="F209" t="s">
+        <v>105</v>
+      </c>
+      <c r="G209" t="s">
+        <v>262</v>
+      </c>
+      <c r="I209" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>10</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" t="s">
+        <v>12</v>
+      </c>
+      <c r="D210" t="s">
+        <v>248</v>
+      </c>
+      <c r="E210" t="s">
+        <v>106</v>
+      </c>
+      <c r="F210" t="s">
+        <v>107</v>
+      </c>
+      <c r="G210" t="s">
+        <v>259</v>
+      </c>
+      <c r="I210" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>10</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" t="s">
+        <v>12</v>
+      </c>
+      <c r="D211" t="s">
+        <v>248</v>
+      </c>
+      <c r="E211" t="s">
+        <v>223</v>
+      </c>
+      <c r="F211" t="s">
+        <v>224</v>
+      </c>
+      <c r="G211" t="s">
+        <v>259</v>
+      </c>
+      <c r="I211" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>10</v>
+      </c>
+      <c r="B212" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>12</v>
+      </c>
+      <c r="D212" t="s">
+        <v>248</v>
+      </c>
+      <c r="E212" t="s">
+        <v>110</v>
+      </c>
+      <c r="F212" t="s">
+        <v>111</v>
+      </c>
+      <c r="G212" t="s">
+        <v>255</v>
+      </c>
+      <c r="I212" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>10</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>12</v>
+      </c>
+      <c r="D213" t="s">
+        <v>248</v>
+      </c>
+      <c r="E213" t="s">
+        <v>229</v>
+      </c>
+      <c r="F213" t="s">
+        <v>230</v>
+      </c>
+      <c r="G213" t="s">
+        <v>268</v>
+      </c>
+      <c r="I213" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>10</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" t="s">
+        <v>12</v>
+      </c>
+      <c r="D214" t="s">
+        <v>248</v>
+      </c>
+      <c r="E214" t="s">
+        <v>269</v>
+      </c>
+      <c r="F214" t="s">
+        <v>270</v>
+      </c>
+      <c r="G214" t="s">
+        <v>271</v>
+      </c>
+      <c r="I214" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>10</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>12</v>
+      </c>
+      <c r="D215" t="s">
+        <v>248</v>
+      </c>
+      <c r="E215" t="s">
+        <v>231</v>
+      </c>
+      <c r="F215" t="s">
+        <v>232</v>
+      </c>
+      <c r="G215" t="s">
+        <v>262</v>
+      </c>
+      <c r="I215" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>10</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216" t="s">
+        <v>248</v>
+      </c>
+      <c r="E216" t="s">
+        <v>272</v>
+      </c>
+      <c r="F216" t="s">
+        <v>273</v>
+      </c>
+      <c r="G216" t="s">
+        <v>255</v>
+      </c>
+      <c r="I216" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>10</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>12</v>
+      </c>
+      <c r="D217" t="s">
+        <v>248</v>
+      </c>
+      <c r="E217" t="s">
+        <v>164</v>
+      </c>
+      <c r="F217" t="s">
+        <v>233</v>
+      </c>
+      <c r="G217" t="s">
+        <v>262</v>
+      </c>
+      <c r="H217" t="s">
+        <v>262</v>
+      </c>
+      <c r="I217" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>10</v>
+      </c>
+      <c r="B218" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218" t="s">
+        <v>12</v>
+      </c>
+      <c r="D218" t="s">
+        <v>248</v>
+      </c>
+      <c r="E218" t="s">
+        <v>234</v>
+      </c>
+      <c r="F218" t="s">
+        <v>235</v>
+      </c>
+      <c r="G218" t="s">
+        <v>262</v>
+      </c>
+      <c r="H218" t="s">
+        <v>262</v>
+      </c>
+      <c r="I218" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>10</v>
+      </c>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" t="s">
+        <v>12</v>
+      </c>
+      <c r="D219" t="s">
+        <v>248</v>
+      </c>
+      <c r="E219" t="s">
+        <v>119</v>
+      </c>
+      <c r="F219" t="s">
+        <v>120</v>
+      </c>
+      <c r="G219" t="s">
+        <v>274</v>
+      </c>
+      <c r="H219" t="s">
+        <v>274</v>
+      </c>
+      <c r="I219" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>10</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" t="s">
+        <v>12</v>
+      </c>
+      <c r="D220" t="s">
+        <v>248</v>
+      </c>
+      <c r="E220" t="s">
         <v>238</v>
       </c>
-      <c r="G185" t="s">
+      <c r="F220" t="s">
+        <v>185</v>
+      </c>
+      <c r="G220" t="s">
+        <v>274</v>
+      </c>
+      <c r="H220" t="s">
+        <v>274</v>
+      </c>
+      <c r="I220" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>10</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221" t="s">
+        <v>248</v>
+      </c>
+      <c r="E221" t="s">
+        <v>122</v>
+      </c>
+      <c r="F221" t="s">
+        <v>123</v>
+      </c>
+      <c r="G221" t="s">
+        <v>275</v>
+      </c>
+      <c r="I221" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>10</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222" t="s">
+        <v>248</v>
+      </c>
+      <c r="E222" t="s">
+        <v>124</v>
+      </c>
+      <c r="F222" t="s">
+        <v>125</v>
+      </c>
+      <c r="G222" t="s">
+        <v>276</v>
+      </c>
+      <c r="I222" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>10</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" t="s">
+        <v>12</v>
+      </c>
+      <c r="D223" t="s">
+        <v>248</v>
+      </c>
+      <c r="E223" t="s">
+        <v>241</v>
+      </c>
+      <c r="F223" t="s">
+        <v>242</v>
+      </c>
+      <c r="G223" t="s">
+        <v>259</v>
+      </c>
+      <c r="H223" t="s">
+        <v>277</v>
+      </c>
+      <c r="I223" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>10</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" t="s">
+        <v>12</v>
+      </c>
+      <c r="D224" t="s">
+        <v>248</v>
+      </c>
+      <c r="E224" t="s">
+        <v>244</v>
+      </c>
+      <c r="F224" t="s">
+        <v>245</v>
+      </c>
+      <c r="G224" t="s">
+        <v>260</v>
+      </c>
+      <c r="H224" t="s">
+        <v>278</v>
+      </c>
+      <c r="I224" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>10</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" t="s">
+        <v>12</v>
+      </c>
+      <c r="D225" t="s">
+        <v>248</v>
+      </c>
+      <c r="E225" t="s">
+        <v>126</v>
+      </c>
+      <c r="F225" t="s">
+        <v>127</v>
+      </c>
+      <c r="G225" t="s">
+        <v>279</v>
+      </c>
+      <c r="H225" t="s">
+        <v>280</v>
+      </c>
+      <c r="I225" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>10</v>
+      </c>
+      <c r="B226" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" t="s">
+        <v>12</v>
+      </c>
+      <c r="D226" t="s">
+        <v>248</v>
+      </c>
+      <c r="E226" t="s">
+        <v>130</v>
+      </c>
+      <c r="F226" t="s">
+        <v>131</v>
+      </c>
+      <c r="G226" t="s">
+        <v>279</v>
+      </c>
+      <c r="H226" t="s">
+        <v>280</v>
+      </c>
+      <c r="I226" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>10</v>
+      </c>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" t="s">
+        <v>12</v>
+      </c>
+      <c r="D227" t="s">
+        <v>248</v>
+      </c>
+      <c r="E227" t="s">
+        <v>132</v>
+      </c>
+      <c r="F227" t="s">
+        <v>133</v>
+      </c>
+      <c r="G227" t="s">
+        <v>279</v>
+      </c>
+      <c r="I227" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>10</v>
+      </c>
+      <c r="B228" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228" t="s">
+        <v>248</v>
+      </c>
+      <c r="E228" t="s">
+        <v>134</v>
+      </c>
+      <c r="F228" t="s">
+        <v>133</v>
+      </c>
+      <c r="G228" t="s">
+        <v>279</v>
+      </c>
+      <c r="H228" t="s">
+        <v>280</v>
+      </c>
+      <c r="I228" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>10</v>
+      </c>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" t="s">
+        <v>12</v>
+      </c>
+      <c r="D229" t="s">
+        <v>248</v>
+      </c>
+      <c r="E229" t="s">
+        <v>135</v>
+      </c>
+      <c r="F229" t="s">
+        <v>136</v>
+      </c>
+      <c r="G229" t="s">
+        <v>279</v>
+      </c>
+      <c r="H229" t="s">
+        <v>280</v>
+      </c>
+      <c r="I229" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>10</v>
+      </c>
+      <c r="B230" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" t="s">
+        <v>12</v>
+      </c>
+      <c r="D230" t="s">
+        <v>281</v>
+      </c>
+      <c r="E230" t="s">
+        <v>18</v>
+      </c>
+      <c r="F230" t="s">
+        <v>19</v>
+      </c>
+      <c r="G230" t="s">
+        <v>20</v>
+      </c>
+      <c r="I230" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>10</v>
+      </c>
+      <c r="B231" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231" t="s">
+        <v>12</v>
+      </c>
+      <c r="D231" t="s">
+        <v>281</v>
+      </c>
+      <c r="E231" t="s">
+        <v>21</v>
+      </c>
+      <c r="F231" t="s">
+        <v>22</v>
+      </c>
+      <c r="G231" t="s">
+        <v>16</v>
+      </c>
+      <c r="I231" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>10</v>
+      </c>
+      <c r="B232" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232" t="s">
+        <v>12</v>
+      </c>
+      <c r="D232" t="s">
+        <v>281</v>
+      </c>
+      <c r="E232" t="s">
+        <v>143</v>
+      </c>
+      <c r="F232" t="s">
+        <v>120</v>
+      </c>
+      <c r="G232" t="s">
+        <v>16</v>
+      </c>
+      <c r="I232" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>10</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233" t="s">
+        <v>281</v>
+      </c>
+      <c r="E233" t="s">
+        <v>26</v>
+      </c>
+      <c r="F233" t="s">
+        <v>22</v>
+      </c>
+      <c r="G233" t="s">
+        <v>16</v>
+      </c>
+      <c r="I233" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>10</v>
+      </c>
+      <c r="B234" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234" t="s">
+        <v>12</v>
+      </c>
+      <c r="D234" t="s">
+        <v>281</v>
+      </c>
+      <c r="E234" t="s">
+        <v>38</v>
+      </c>
+      <c r="F234" t="s">
+        <v>282</v>
+      </c>
+      <c r="G234" t="s">
+        <v>16</v>
+      </c>
+      <c r="I234" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>10</v>
+      </c>
+      <c r="B235" t="s">
+        <v>11</v>
+      </c>
+      <c r="C235" t="s">
+        <v>12</v>
+      </c>
+      <c r="D235" t="s">
+        <v>281</v>
+      </c>
+      <c r="E235" t="s">
+        <v>151</v>
+      </c>
+      <c r="F235" t="s">
+        <v>283</v>
+      </c>
+      <c r="G235" t="s">
+        <v>16</v>
+      </c>
+      <c r="I235" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>74</v>
+      </c>
+      <c r="B236" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236" t="s">
+        <v>12</v>
+      </c>
+      <c r="D236" t="s">
+        <v>281</v>
+      </c>
+      <c r="E236" t="s">
+        <v>154</v>
+      </c>
+      <c r="F236" t="s">
+        <v>171</v>
+      </c>
+      <c r="G236" t="s">
+        <v>262</v>
+      </c>
+      <c r="I236" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>10</v>
+      </c>
+      <c r="B237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237" t="s">
+        <v>12</v>
+      </c>
+      <c r="D237" t="s">
+        <v>281</v>
+      </c>
+      <c r="E237" t="s">
+        <v>47</v>
+      </c>
+      <c r="F237" t="s">
+        <v>173</v>
+      </c>
+      <c r="G237" t="s">
+        <v>16</v>
+      </c>
+      <c r="I237" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>74</v>
+      </c>
+      <c r="B238" t="s">
+        <v>11</v>
+      </c>
+      <c r="C238" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" t="s">
+        <v>281</v>
+      </c>
+      <c r="E238" t="s">
+        <v>156</v>
+      </c>
+      <c r="F238" t="s">
+        <v>284</v>
+      </c>
+      <c r="G238" t="s">
+        <v>259</v>
+      </c>
+      <c r="I238" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>10</v>
+      </c>
+      <c r="B239" t="s">
+        <v>11</v>
+      </c>
+      <c r="C239" t="s">
+        <v>12</v>
+      </c>
+      <c r="D239" t="s">
+        <v>281</v>
+      </c>
+      <c r="E239" t="s">
+        <v>158</v>
+      </c>
+      <c r="F239" t="s">
+        <v>176</v>
+      </c>
+      <c r="G239" t="s">
+        <v>16</v>
+      </c>
+      <c r="I239" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>10</v>
+      </c>
+      <c r="B240" t="s">
+        <v>11</v>
+      </c>
+      <c r="C240" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" t="s">
+        <v>281</v>
+      </c>
+      <c r="E240" t="s">
+        <v>49</v>
+      </c>
+      <c r="F240" t="s">
+        <v>50</v>
+      </c>
+      <c r="G240" t="s">
+        <v>16</v>
+      </c>
+      <c r="I240" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>10</v>
+      </c>
+      <c r="B241" t="s">
+        <v>11</v>
+      </c>
+      <c r="C241" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" t="s">
+        <v>281</v>
+      </c>
+      <c r="E241" t="s">
+        <v>68</v>
+      </c>
+      <c r="F241" t="s">
+        <v>105</v>
+      </c>
+      <c r="G241" t="s">
+        <v>16</v>
+      </c>
+      <c r="I241" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>10</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
+        <v>281</v>
+      </c>
+      <c r="E242" t="s">
+        <v>70</v>
+      </c>
+      <c r="F242" t="s">
+        <v>71</v>
+      </c>
+      <c r="G242" t="s">
+        <v>16</v>
+      </c>
+      <c r="I242" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>74</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243" t="s">
+        <v>12</v>
+      </c>
+      <c r="D243" t="s">
+        <v>281</v>
+      </c>
+      <c r="E243" t="s">
+        <v>285</v>
+      </c>
+      <c r="F243" t="s">
+        <v>232</v>
+      </c>
+      <c r="G243" t="s">
+        <v>262</v>
+      </c>
+      <c r="I243" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>74</v>
+      </c>
+      <c r="B244" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" t="s">
+        <v>12</v>
+      </c>
+      <c r="D244" t="s">
+        <v>281</v>
+      </c>
+      <c r="E244" t="s">
+        <v>286</v>
+      </c>
+      <c r="F244" t="s">
+        <v>188</v>
+      </c>
+      <c r="G244" t="s">
+        <v>16</v>
+      </c>
+      <c r="I244" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>74</v>
+      </c>
+      <c r="B245" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245" t="s">
+        <v>12</v>
+      </c>
+      <c r="D245" t="s">
+        <v>281</v>
+      </c>
+      <c r="E245" t="s">
+        <v>186</v>
+      </c>
+      <c r="F245" t="s">
+        <v>190</v>
+      </c>
+      <c r="G245" t="s">
+        <v>16</v>
+      </c>
+      <c r="I245" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>74</v>
+      </c>
+      <c r="B246" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" t="s">
+        <v>12</v>
+      </c>
+      <c r="D246" t="s">
+        <v>281</v>
+      </c>
+      <c r="E246" t="s">
+        <v>265</v>
+      </c>
+      <c r="F246" t="s">
+        <v>78</v>
+      </c>
+      <c r="G246" t="s">
+        <v>260</v>
+      </c>
+      <c r="I246" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>10</v>
+      </c>
+      <c r="B247" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247" t="s">
+        <v>12</v>
+      </c>
+      <c r="D247" t="s">
+        <v>281</v>
+      </c>
+      <c r="E247" t="s">
+        <v>75</v>
+      </c>
+      <c r="F247" t="s">
+        <v>188</v>
+      </c>
+      <c r="G247" t="s">
+        <v>16</v>
+      </c>
+      <c r="I247" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>10</v>
+      </c>
+      <c r="B248" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" t="s">
+        <v>12</v>
+      </c>
+      <c r="D248" t="s">
+        <v>281</v>
+      </c>
+      <c r="E248" t="s">
+        <v>189</v>
+      </c>
+      <c r="F248" t="s">
+        <v>190</v>
+      </c>
+      <c r="G248" t="s">
+        <v>16</v>
+      </c>
+      <c r="I248" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>10</v>
+      </c>
+      <c r="B249" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" t="s">
+        <v>12</v>
+      </c>
+      <c r="D249" t="s">
+        <v>281</v>
+      </c>
+      <c r="E249" t="s">
+        <v>191</v>
+      </c>
+      <c r="F249" t="s">
         <v>192</v>
       </c>
-      <c r="I185" t="s">
+      <c r="G249" t="s">
+        <v>16</v>
+      </c>
+      <c r="I249" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>10</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" t="s">
+        <v>12</v>
+      </c>
+      <c r="D250" t="s">
+        <v>281</v>
+      </c>
+      <c r="E250" t="s">
+        <v>77</v>
+      </c>
+      <c r="F250" t="s">
+        <v>78</v>
+      </c>
+      <c r="G250" t="s">
+        <v>16</v>
+      </c>
+      <c r="I250" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>10</v>
+      </c>
+      <c r="B251" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" t="s">
+        <v>12</v>
+      </c>
+      <c r="D251" t="s">
+        <v>281</v>
+      </c>
+      <c r="E251" t="s">
+        <v>194</v>
+      </c>
+      <c r="F251" t="s">
+        <v>195</v>
+      </c>
+      <c r="G251" t="s">
+        <v>16</v>
+      </c>
+      <c r="I251" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>10</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252" t="s">
+        <v>12</v>
+      </c>
+      <c r="D252" t="s">
+        <v>281</v>
+      </c>
+      <c r="E252" t="s">
+        <v>196</v>
+      </c>
+      <c r="F252" t="s">
+        <v>197</v>
+      </c>
+      <c r="G252" t="s">
+        <v>16</v>
+      </c>
+      <c r="I252" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>10</v>
+      </c>
+      <c r="B253" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" t="s">
+        <v>12</v>
+      </c>
+      <c r="D253" t="s">
+        <v>281</v>
+      </c>
+      <c r="E253" t="s">
+        <v>82</v>
+      </c>
+      <c r="F253" t="s">
+        <v>50</v>
+      </c>
+      <c r="G253" t="s">
+        <v>16</v>
+      </c>
+      <c r="I253" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>10</v>
+      </c>
+      <c r="B254" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" t="s">
+        <v>12</v>
+      </c>
+      <c r="D254" t="s">
+        <v>281</v>
+      </c>
+      <c r="E254" t="s">
+        <v>83</v>
+      </c>
+      <c r="F254" t="s">
+        <v>84</v>
+      </c>
+      <c r="G254" t="s">
+        <v>16</v>
+      </c>
+      <c r="I254" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>10</v>
+      </c>
+      <c r="B255" t="s">
+        <v>11</v>
+      </c>
+      <c r="C255" t="s">
+        <v>12</v>
+      </c>
+      <c r="D255" t="s">
+        <v>281</v>
+      </c>
+      <c r="E255" t="s">
+        <v>85</v>
+      </c>
+      <c r="F255" t="s">
+        <v>86</v>
+      </c>
+      <c r="G255" t="s">
+        <v>16</v>
+      </c>
+      <c r="I255" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>10</v>
+      </c>
+      <c r="B256" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256" t="s">
+        <v>12</v>
+      </c>
+      <c r="D256" t="s">
+        <v>281</v>
+      </c>
+      <c r="E256" t="s">
+        <v>202</v>
+      </c>
+      <c r="F256" t="s">
+        <v>203</v>
+      </c>
+      <c r="G256" t="s">
+        <v>16</v>
+      </c>
+      <c r="I256" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>10</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" t="s">
+        <v>12</v>
+      </c>
+      <c r="D257" t="s">
+        <v>281</v>
+      </c>
+      <c r="E257" t="s">
+        <v>204</v>
+      </c>
+      <c r="F257" t="s">
+        <v>205</v>
+      </c>
+      <c r="G257" t="s">
+        <v>16</v>
+      </c>
+      <c r="I257" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>10</v>
+      </c>
+      <c r="B258" t="s">
+        <v>11</v>
+      </c>
+      <c r="C258" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" t="s">
+        <v>281</v>
+      </c>
+      <c r="E258" t="s">
+        <v>92</v>
+      </c>
+      <c r="F258" t="s">
+        <v>93</v>
+      </c>
+      <c r="G258" t="s">
+        <v>16</v>
+      </c>
+      <c r="I258" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>10</v>
+      </c>
+      <c r="B259" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259" t="s">
+        <v>12</v>
+      </c>
+      <c r="D259" t="s">
+        <v>281</v>
+      </c>
+      <c r="E259" t="s">
+        <v>208</v>
+      </c>
+      <c r="F259" t="s">
+        <v>209</v>
+      </c>
+      <c r="G259" t="s">
+        <v>16</v>
+      </c>
+      <c r="I259" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>10</v>
+      </c>
+      <c r="B260" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" t="s">
+        <v>12</v>
+      </c>
+      <c r="D260" t="s">
+        <v>281</v>
+      </c>
+      <c r="E260" t="s">
+        <v>210</v>
+      </c>
+      <c r="F260" t="s">
+        <v>211</v>
+      </c>
+      <c r="G260" t="s">
+        <v>16</v>
+      </c>
+      <c r="I260" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>10</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" t="s">
+        <v>281</v>
+      </c>
+      <c r="E261" t="s">
+        <v>216</v>
+      </c>
+      <c r="F261" t="s">
+        <v>217</v>
+      </c>
+      <c r="G261" t="s">
+        <v>16</v>
+      </c>
+      <c r="I261" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>10</v>
+      </c>
+      <c r="B262" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262" t="s">
+        <v>12</v>
+      </c>
+      <c r="D262" t="s">
+        <v>281</v>
+      </c>
+      <c r="E262" t="s">
+        <v>219</v>
+      </c>
+      <c r="F262" t="s">
+        <v>220</v>
+      </c>
+      <c r="G262" t="s">
+        <v>16</v>
+      </c>
+      <c r="I262" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>10</v>
+      </c>
+      <c r="B263" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263" t="s">
+        <v>12</v>
+      </c>
+      <c r="D263" t="s">
+        <v>281</v>
+      </c>
+      <c r="E263" t="s">
+        <v>104</v>
+      </c>
+      <c r="F263" t="s">
+        <v>105</v>
+      </c>
+      <c r="G263" t="s">
+        <v>16</v>
+      </c>
+      <c r="I263" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>10</v>
+      </c>
+      <c r="B264" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" t="s">
+        <v>12</v>
+      </c>
+      <c r="D264" t="s">
+        <v>281</v>
+      </c>
+      <c r="E264" t="s">
+        <v>106</v>
+      </c>
+      <c r="F264" t="s">
+        <v>107</v>
+      </c>
+      <c r="G264" t="s">
+        <v>16</v>
+      </c>
+      <c r="I264" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>10</v>
+      </c>
+      <c r="B265" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" t="s">
+        <v>12</v>
+      </c>
+      <c r="D265" t="s">
+        <v>281</v>
+      </c>
+      <c r="E265" t="s">
+        <v>223</v>
+      </c>
+      <c r="F265" t="s">
+        <v>224</v>
+      </c>
+      <c r="G265" t="s">
+        <v>16</v>
+      </c>
+      <c r="I265" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>10</v>
+      </c>
+      <c r="B266" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" t="s">
+        <v>281</v>
+      </c>
+      <c r="E266" t="s">
+        <v>227</v>
+      </c>
+      <c r="F266" t="s">
+        <v>228</v>
+      </c>
+      <c r="G266" t="s">
+        <v>16</v>
+      </c>
+      <c r="I266" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>10</v>
+      </c>
+      <c r="B267" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267" t="s">
+        <v>12</v>
+      </c>
+      <c r="D267" t="s">
+        <v>281</v>
+      </c>
+      <c r="E267" t="s">
+        <v>229</v>
+      </c>
+      <c r="F267" t="s">
+        <v>230</v>
+      </c>
+      <c r="G267" t="s">
+        <v>16</v>
+      </c>
+      <c r="I267" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>10</v>
+      </c>
+      <c r="B268" t="s">
+        <v>11</v>
+      </c>
+      <c r="C268" t="s">
+        <v>12</v>
+      </c>
+      <c r="D268" t="s">
+        <v>281</v>
+      </c>
+      <c r="E268" t="s">
+        <v>231</v>
+      </c>
+      <c r="F268" t="s">
+        <v>232</v>
+      </c>
+      <c r="G268" t="s">
+        <v>16</v>
+      </c>
+      <c r="I268" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>10</v>
+      </c>
+      <c r="B269" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269" t="s">
+        <v>12</v>
+      </c>
+      <c r="D269" t="s">
+        <v>281</v>
+      </c>
+      <c r="E269" t="s">
+        <v>164</v>
+      </c>
+      <c r="F269" t="s">
+        <v>233</v>
+      </c>
+      <c r="G269" t="s">
+        <v>16</v>
+      </c>
+      <c r="H269" t="s">
+        <v>16</v>
+      </c>
+      <c r="I269" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>10</v>
+      </c>
+      <c r="B270" t="s">
+        <v>11</v>
+      </c>
+      <c r="C270" t="s">
+        <v>12</v>
+      </c>
+      <c r="D270" t="s">
+        <v>281</v>
+      </c>
+      <c r="E270" t="s">
+        <v>234</v>
+      </c>
+      <c r="F270" t="s">
+        <v>235</v>
+      </c>
+      <c r="G270" t="s">
+        <v>16</v>
+      </c>
+      <c r="H270" t="s">
+        <v>16</v>
+      </c>
+      <c r="I270" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>10</v>
+      </c>
+      <c r="B271" t="s">
+        <v>11</v>
+      </c>
+      <c r="C271" t="s">
+        <v>12</v>
+      </c>
+      <c r="D271" t="s">
+        <v>281</v>
+      </c>
+      <c r="E271" t="s">
+        <v>119</v>
+      </c>
+      <c r="F271" t="s">
+        <v>120</v>
+      </c>
+      <c r="G271" t="s">
+        <v>16</v>
+      </c>
+      <c r="H271" t="s">
+        <v>16</v>
+      </c>
+      <c r="I271" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>10</v>
+      </c>
+      <c r="B272" t="s">
+        <v>11</v>
+      </c>
+      <c r="C272" t="s">
+        <v>12</v>
+      </c>
+      <c r="D272" t="s">
+        <v>281</v>
+      </c>
+      <c r="E272" t="s">
         <v>238</v>
       </c>
+      <c r="F272" t="s">
+        <v>185</v>
+      </c>
+      <c r="G272" t="s">
+        <v>16</v>
+      </c>
+      <c r="H272" t="s">
+        <v>16</v>
+      </c>
+      <c r="I272" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>10</v>
+      </c>
+      <c r="B273" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" t="s">
+        <v>12</v>
+      </c>
+      <c r="D273" t="s">
+        <v>281</v>
+      </c>
+      <c r="E273" t="s">
+        <v>122</v>
+      </c>
+      <c r="F273" t="s">
+        <v>123</v>
+      </c>
+      <c r="G273" t="s">
+        <v>16</v>
+      </c>
+      <c r="I273" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>10</v>
+      </c>
+      <c r="B274" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" t="s">
+        <v>12</v>
+      </c>
+      <c r="D274" t="s">
+        <v>281</v>
+      </c>
+      <c r="E274" t="s">
+        <v>124</v>
+      </c>
+      <c r="F274" t="s">
+        <v>125</v>
+      </c>
+      <c r="G274" t="s">
+        <v>16</v>
+      </c>
+      <c r="I274" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>10</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" t="s">
+        <v>12</v>
+      </c>
+      <c r="D275" t="s">
+        <v>281</v>
+      </c>
+      <c r="E275" t="s">
+        <v>241</v>
+      </c>
+      <c r="F275" t="s">
+        <v>242</v>
+      </c>
+      <c r="G275" t="s">
+        <v>16</v>
+      </c>
+      <c r="H275" t="s">
+        <v>16</v>
+      </c>
+      <c r="I275" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>10</v>
+      </c>
+      <c r="B276" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276" t="s">
+        <v>12</v>
+      </c>
+      <c r="D276" t="s">
+        <v>281</v>
+      </c>
+      <c r="E276" t="s">
+        <v>244</v>
+      </c>
+      <c r="F276" t="s">
+        <v>245</v>
+      </c>
+      <c r="G276" t="s">
+        <v>16</v>
+      </c>
+      <c r="H276" t="s">
+        <v>16</v>
+      </c>
+      <c r="I276" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>10</v>
+      </c>
+      <c r="B277" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277" t="s">
+        <v>12</v>
+      </c>
+      <c r="D277" t="s">
+        <v>281</v>
+      </c>
+      <c r="E277" t="s">
+        <v>126</v>
+      </c>
+      <c r="F277" t="s">
+        <v>127</v>
+      </c>
+      <c r="G277" t="s">
+        <v>16</v>
+      </c>
+      <c r="H277" t="s">
+        <v>16</v>
+      </c>
+      <c r="I277" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>10</v>
+      </c>
+      <c r="B278" t="s">
+        <v>11</v>
+      </c>
+      <c r="C278" t="s">
+        <v>12</v>
+      </c>
+      <c r="D278" t="s">
+        <v>281</v>
+      </c>
+      <c r="E278" t="s">
+        <v>130</v>
+      </c>
+      <c r="F278" t="s">
+        <v>131</v>
+      </c>
+      <c r="G278" t="s">
+        <v>16</v>
+      </c>
+      <c r="H278" t="s">
+        <v>16</v>
+      </c>
+      <c r="I278" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>10</v>
+      </c>
+      <c r="B279" t="s">
+        <v>11</v>
+      </c>
+      <c r="C279" t="s">
+        <v>12</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+      <c r="E279" t="s">
+        <v>132</v>
+      </c>
+      <c r="F279" t="s">
+        <v>133</v>
+      </c>
+      <c r="G279" t="s">
+        <v>16</v>
+      </c>
+      <c r="I279" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>10</v>
+      </c>
+      <c r="B280" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280" t="s">
+        <v>12</v>
+      </c>
+      <c r="D280" t="s">
+        <v>281</v>
+      </c>
+      <c r="E280" t="s">
+        <v>134</v>
+      </c>
+      <c r="F280" t="s">
+        <v>133</v>
+      </c>
+      <c r="G280" t="s">
+        <v>16</v>
+      </c>
+      <c r="H280" t="s">
+        <v>16</v>
+      </c>
+      <c r="I280" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>10</v>
+      </c>
+      <c r="B281" t="s">
+        <v>11</v>
+      </c>
+      <c r="C281" t="s">
+        <v>12</v>
+      </c>
+      <c r="D281" t="s">
+        <v>281</v>
+      </c>
+      <c r="E281" t="s">
+        <v>135</v>
+      </c>
+      <c r="F281" t="s">
+        <v>136</v>
+      </c>
+      <c r="G281" t="s">
+        <v>16</v>
+      </c>
+      <c r="H281" t="s">
+        <v>16</v>
+      </c>
+      <c r="I281" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>10</v>
+      </c>
+      <c r="B282" t="s">
+        <v>287</v>
+      </c>
+      <c r="C282" t="s">
+        <v>288</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="F282" t="s">
+        <v>127</v>
+      </c>
+      <c r="G282" t="s">
+        <v>289</v>
+      </c>
+      <c r="I282" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>10</v>
+      </c>
+      <c r="B283" t="s">
+        <v>287</v>
+      </c>
+      <c r="C283" t="s">
+        <v>288</v>
+      </c>
+      <c r="E283" t="s">
+        <v>128</v>
+      </c>
+      <c r="F283" t="s">
+        <v>129</v>
+      </c>
+      <c r="G283" t="s">
+        <v>289</v>
+      </c>
+      <c r="I283" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>10</v>
+      </c>
+      <c r="B284" t="s">
+        <v>287</v>
+      </c>
+      <c r="C284" t="s">
+        <v>288</v>
+      </c>
+      <c r="E284" t="s">
+        <v>130</v>
+      </c>
+      <c r="F284" t="s">
+        <v>131</v>
+      </c>
+      <c r="G284" t="s">
+        <v>289</v>
+      </c>
+      <c r="I284" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>10</v>
+      </c>
+      <c r="B285" t="s">
+        <v>287</v>
+      </c>
+      <c r="C285" t="s">
+        <v>288</v>
+      </c>
+      <c r="E285" t="s">
+        <v>165</v>
+      </c>
+      <c r="F285" t="s">
+        <v>133</v>
+      </c>
+      <c r="G285" t="s">
+        <v>289</v>
+      </c>
+      <c r="I285" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>10</v>
+      </c>
+      <c r="B286" t="s">
+        <v>287</v>
+      </c>
+      <c r="C286" t="s">
+        <v>288</v>
+      </c>
+      <c r="E286" t="s">
+        <v>132</v>
+      </c>
+      <c r="F286" t="s">
+        <v>136</v>
+      </c>
+      <c r="G286" t="s">
+        <v>289</v>
+      </c>
+      <c r="I286" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>10</v>
+      </c>
+      <c r="B287" t="s">
+        <v>287</v>
+      </c>
+      <c r="C287" t="s">
+        <v>288</v>
+      </c>
+      <c r="E287" t="s">
+        <v>134</v>
+      </c>
+      <c r="F287" t="s">
+        <v>133</v>
+      </c>
+      <c r="G287" t="s">
+        <v>289</v>
+      </c>
+      <c r="I287" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>10</v>
+      </c>
+      <c r="B288" t="s">
+        <v>287</v>
+      </c>
+      <c r="C288" t="s">
+        <v>288</v>
+      </c>
+      <c r="E288" t="s">
+        <v>135</v>
+      </c>
+      <c r="F288" t="s">
+        <v>136</v>
+      </c>
+      <c r="G288" t="s">
+        <v>289</v>
+      </c>
+      <c r="I288" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>10</v>
+      </c>
+      <c r="B289" t="s">
+        <v>287</v>
+      </c>
+      <c r="C289" t="s">
+        <v>290</v>
+      </c>
+      <c r="E289" t="s">
+        <v>291</v>
+      </c>
+      <c r="F289" t="s">
+        <v>292</v>
+      </c>
+      <c r="G289" t="s">
+        <v>289</v>
+      </c>
+      <c r="I289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>10</v>
+      </c>
+      <c r="B290" t="s">
+        <v>287</v>
+      </c>
+      <c r="C290" t="s">
+        <v>290</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+      <c r="G290" t="s">
+        <v>289</v>
+      </c>
+      <c r="I290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>10</v>
+      </c>
+      <c r="B291" t="s">
+        <v>287</v>
+      </c>
+      <c r="C291" t="s">
+        <v>290</v>
+      </c>
+      <c r="E291" t="s">
+        <v>14</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+      <c r="G291" t="s">
+        <v>289</v>
+      </c>
+      <c r="I291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>10</v>
+      </c>
+      <c r="B292" t="s">
+        <v>287</v>
+      </c>
+      <c r="C292" t="s">
+        <v>290</v>
+      </c>
+      <c r="E292" t="s">
+        <v>18</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+      <c r="G292" t="s">
+        <v>289</v>
+      </c>
+      <c r="I292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>10</v>
+      </c>
+      <c r="B293" t="s">
+        <v>287</v>
+      </c>
+      <c r="C293" t="s">
+        <v>290</v>
+      </c>
+      <c r="E293" t="s">
+        <v>21</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+      <c r="G293" t="s">
+        <v>289</v>
+      </c>
+      <c r="I293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>10</v>
+      </c>
+      <c r="B294" t="s">
+        <v>287</v>
+      </c>
+      <c r="C294" t="s">
+        <v>290</v>
+      </c>
+      <c r="E294" t="s">
+        <v>141</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+      <c r="G294" t="s">
+        <v>289</v>
+      </c>
+      <c r="I294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>10</v>
+      </c>
+      <c r="B295" t="s">
+        <v>287</v>
+      </c>
+      <c r="C295" t="s">
+        <v>290</v>
+      </c>
+      <c r="E295" t="s">
+        <v>24</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+      <c r="G295" t="s">
+        <v>289</v>
+      </c>
+      <c r="I295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>10</v>
+      </c>
+      <c r="B296" t="s">
+        <v>287</v>
+      </c>
+      <c r="C296" t="s">
+        <v>290</v>
+      </c>
+      <c r="E296" t="s">
+        <v>143</v>
+      </c>
+      <c r="F296" t="s">
+        <v>295</v>
+      </c>
+      <c r="G296" t="s">
+        <v>289</v>
+      </c>
+      <c r="I296" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>10</v>
+      </c>
+      <c r="B297" t="s">
+        <v>287</v>
+      </c>
+      <c r="C297" t="s">
+        <v>290</v>
+      </c>
+      <c r="E297" t="s">
+        <v>145</v>
+      </c>
+      <c r="F297" t="s">
+        <v>300</v>
+      </c>
+      <c r="G297" t="s">
+        <v>289</v>
+      </c>
+      <c r="I297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>10</v>
+      </c>
+      <c r="B298" t="s">
+        <v>287</v>
+      </c>
+      <c r="C298" t="s">
+        <v>290</v>
+      </c>
+      <c r="E298" t="s">
+        <v>27</v>
+      </c>
+      <c r="F298" t="s">
+        <v>301</v>
+      </c>
+      <c r="G298" t="s">
+        <v>289</v>
+      </c>
+      <c r="I298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>10</v>
+      </c>
+      <c r="B299" t="s">
+        <v>287</v>
+      </c>
+      <c r="C299" t="s">
+        <v>290</v>
+      </c>
+      <c r="E299" t="s">
+        <v>29</v>
+      </c>
+      <c r="F299" t="s">
+        <v>302</v>
+      </c>
+      <c r="G299" t="s">
+        <v>289</v>
+      </c>
+      <c r="I299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>10</v>
+      </c>
+      <c r="B300" t="s">
+        <v>287</v>
+      </c>
+      <c r="C300" t="s">
+        <v>290</v>
+      </c>
+      <c r="E300" t="s">
+        <v>30</v>
+      </c>
+      <c r="F300" t="s">
+        <v>303</v>
+      </c>
+      <c r="G300" t="s">
+        <v>289</v>
+      </c>
+      <c r="I300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>10</v>
+      </c>
+      <c r="B301" t="s">
+        <v>287</v>
+      </c>
+      <c r="C301" t="s">
+        <v>290</v>
+      </c>
+      <c r="E301" t="s">
+        <v>35</v>
+      </c>
+      <c r="F301" t="s">
+        <v>304</v>
+      </c>
+      <c r="G301" t="s">
+        <v>289</v>
+      </c>
+      <c r="I301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>10</v>
+      </c>
+      <c r="B302" t="s">
+        <v>287</v>
+      </c>
+      <c r="C302" t="s">
+        <v>290</v>
+      </c>
+      <c r="E302" t="s">
+        <v>38</v>
+      </c>
+      <c r="F302" t="s">
+        <v>305</v>
+      </c>
+      <c r="G302" t="s">
+        <v>289</v>
+      </c>
+      <c r="I302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>10</v>
+      </c>
+      <c r="B303" t="s">
+        <v>287</v>
+      </c>
+      <c r="C303" t="s">
+        <v>290</v>
+      </c>
+      <c r="E303" t="s">
+        <v>151</v>
+      </c>
+      <c r="F303" t="s">
+        <v>306</v>
+      </c>
+      <c r="G303" t="s">
+        <v>289</v>
+      </c>
+      <c r="I303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>10</v>
+      </c>
+      <c r="B304" t="s">
+        <v>287</v>
+      </c>
+      <c r="C304" t="s">
+        <v>290</v>
+      </c>
+      <c r="E304" t="s">
+        <v>45</v>
+      </c>
+      <c r="F304" t="s">
+        <v>307</v>
+      </c>
+      <c r="G304" t="s">
+        <v>289</v>
+      </c>
+      <c r="I304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>10</v>
+      </c>
+      <c r="B305" t="s">
+        <v>287</v>
+      </c>
+      <c r="C305" t="s">
+        <v>290</v>
+      </c>
+      <c r="E305" t="s">
+        <v>154</v>
+      </c>
+      <c r="F305" t="s">
+        <v>308</v>
+      </c>
+      <c r="G305" t="s">
+        <v>289</v>
+      </c>
+      <c r="I305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>10</v>
+      </c>
+      <c r="B306" t="s">
+        <v>287</v>
+      </c>
+      <c r="C306" t="s">
+        <v>290</v>
+      </c>
+      <c r="E306" t="s">
+        <v>47</v>
+      </c>
+      <c r="F306" t="s">
+        <v>309</v>
+      </c>
+      <c r="G306" t="s">
+        <v>289</v>
+      </c>
+      <c r="I306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>10</v>
+      </c>
+      <c r="B307" t="s">
+        <v>287</v>
+      </c>
+      <c r="C307" t="s">
+        <v>290</v>
+      </c>
+      <c r="E307" t="s">
+        <v>156</v>
+      </c>
+      <c r="F307" t="s">
+        <v>310</v>
+      </c>
+      <c r="G307" t="s">
+        <v>289</v>
+      </c>
+      <c r="I307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>10</v>
+      </c>
+      <c r="B308" t="s">
+        <v>287</v>
+      </c>
+      <c r="C308" t="s">
+        <v>290</v>
+      </c>
+      <c r="E308" t="s">
+        <v>160</v>
+      </c>
+      <c r="F308" t="s">
+        <v>311</v>
+      </c>
+      <c r="G308" t="s">
+        <v>289</v>
+      </c>
+      <c r="I308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>10</v>
+      </c>
+      <c r="B309" t="s">
+        <v>287</v>
+      </c>
+      <c r="C309" t="s">
+        <v>290</v>
+      </c>
+      <c r="E309" t="s">
+        <v>162</v>
+      </c>
+      <c r="F309" t="s">
+        <v>312</v>
+      </c>
+      <c r="G309" t="s">
+        <v>289</v>
+      </c>
+      <c r="I309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>10</v>
+      </c>
+      <c r="B310" t="s">
+        <v>287</v>
+      </c>
+      <c r="C310" t="s">
+        <v>290</v>
+      </c>
+      <c r="E310" t="s">
+        <v>177</v>
+      </c>
+      <c r="F310" t="s">
+        <v>313</v>
+      </c>
+      <c r="G310" t="s">
+        <v>289</v>
+      </c>
+      <c r="I310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>10</v>
+      </c>
+      <c r="B311" t="s">
+        <v>287</v>
+      </c>
+      <c r="C311" t="s">
+        <v>290</v>
+      </c>
+      <c r="E311" t="s">
+        <v>49</v>
+      </c>
+      <c r="F311" t="s">
+        <v>314</v>
+      </c>
+      <c r="G311" t="s">
+        <v>289</v>
+      </c>
+      <c r="I311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>10</v>
+      </c>
+      <c r="B312" t="s">
+        <v>287</v>
+      </c>
+      <c r="C312" t="s">
+        <v>290</v>
+      </c>
+      <c r="E312" t="s">
+        <v>179</v>
+      </c>
+      <c r="F312" t="s">
+        <v>315</v>
+      </c>
+      <c r="G312" t="s">
+        <v>289</v>
+      </c>
+      <c r="I312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>10</v>
+      </c>
+      <c r="B313" t="s">
+        <v>287</v>
+      </c>
+      <c r="C313" t="s">
+        <v>290</v>
+      </c>
+      <c r="E313" t="s">
+        <v>51</v>
+      </c>
+      <c r="F313" t="s">
+        <v>316</v>
+      </c>
+      <c r="G313" t="s">
+        <v>289</v>
+      </c>
+      <c r="I313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>10</v>
+      </c>
+      <c r="B314" t="s">
+        <v>287</v>
+      </c>
+      <c r="C314" t="s">
+        <v>290</v>
+      </c>
+      <c r="E314" t="s">
+        <v>53</v>
+      </c>
+      <c r="F314" t="s">
+        <v>317</v>
+      </c>
+      <c r="G314" t="s">
+        <v>289</v>
+      </c>
+      <c r="I314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>10</v>
+      </c>
+      <c r="B315" t="s">
+        <v>287</v>
+      </c>
+      <c r="C315" t="s">
+        <v>290</v>
+      </c>
+      <c r="E315" t="s">
+        <v>55</v>
+      </c>
+      <c r="F315" t="s">
+        <v>318</v>
+      </c>
+      <c r="G315" t="s">
+        <v>289</v>
+      </c>
+      <c r="I315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>10</v>
+      </c>
+      <c r="B316" t="s">
+        <v>287</v>
+      </c>
+      <c r="C316" t="s">
+        <v>290</v>
+      </c>
+      <c r="E316" t="s">
+        <v>57</v>
+      </c>
+      <c r="F316" t="s">
+        <v>319</v>
+      </c>
+      <c r="G316" t="s">
+        <v>289</v>
+      </c>
+      <c r="I316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>10</v>
+      </c>
+      <c r="B317" t="s">
+        <v>287</v>
+      </c>
+      <c r="C317" t="s">
+        <v>290</v>
+      </c>
+      <c r="E317" t="s">
+        <v>59</v>
+      </c>
+      <c r="F317" t="s">
+        <v>320</v>
+      </c>
+      <c r="G317" t="s">
+        <v>289</v>
+      </c>
+      <c r="I317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>10</v>
+      </c>
+      <c r="B318" t="s">
+        <v>287</v>
+      </c>
+      <c r="C318" t="s">
+        <v>290</v>
+      </c>
+      <c r="E318" t="s">
+        <v>61</v>
+      </c>
+      <c r="F318" t="s">
+        <v>321</v>
+      </c>
+      <c r="G318" t="s">
+        <v>289</v>
+      </c>
+      <c r="I318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>10</v>
+      </c>
+      <c r="B319" t="s">
+        <v>287</v>
+      </c>
+      <c r="C319" t="s">
+        <v>290</v>
+      </c>
+      <c r="E319" t="s">
+        <v>63</v>
+      </c>
+      <c r="F319" t="s">
+        <v>322</v>
+      </c>
+      <c r="G319" t="s">
+        <v>289</v>
+      </c>
+      <c r="I319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>10</v>
+      </c>
+      <c r="B320" t="s">
+        <v>287</v>
+      </c>
+      <c r="C320" t="s">
+        <v>290</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+      <c r="G320" t="s">
+        <v>289</v>
+      </c>
+      <c r="I320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>10</v>
+      </c>
+      <c r="B321" t="s">
+        <v>287</v>
+      </c>
+      <c r="C321" t="s">
+        <v>290</v>
+      </c>
+      <c r="E321" t="s">
+        <v>325</v>
+      </c>
+      <c r="F321" t="s">
+        <v>326</v>
+      </c>
+      <c r="G321" t="s">
+        <v>289</v>
+      </c>
+      <c r="I321" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>10</v>
+      </c>
+      <c r="B322" t="s">
+        <v>287</v>
+      </c>
+      <c r="C322" t="s">
+        <v>290</v>
+      </c>
+      <c r="E322" t="s">
+        <v>327</v>
+      </c>
+      <c r="F322" t="s">
+        <v>328</v>
+      </c>
+      <c r="G322" t="s">
+        <v>289</v>
+      </c>
+      <c r="I322" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>10</v>
+      </c>
+      <c r="B323" t="s">
+        <v>287</v>
+      </c>
+      <c r="C323" t="s">
+        <v>290</v>
+      </c>
+      <c r="E323" t="s">
+        <v>329</v>
+      </c>
+      <c r="F323" t="s">
+        <v>330</v>
+      </c>
+      <c r="G323" t="s">
+        <v>289</v>
+      </c>
+      <c r="I323" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>10</v>
+      </c>
+      <c r="B324" t="s">
+        <v>287</v>
+      </c>
+      <c r="C324" t="s">
+        <v>290</v>
+      </c>
+      <c r="E324" t="s">
+        <v>331</v>
+      </c>
+      <c r="F324" t="s">
+        <v>332</v>
+      </c>
+      <c r="G324" t="s">
+        <v>289</v>
+      </c>
+      <c r="I324" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>10</v>
+      </c>
+      <c r="B325" t="s">
+        <v>287</v>
+      </c>
+      <c r="C325" t="s">
+        <v>290</v>
+      </c>
+      <c r="E325" t="s">
+        <v>333</v>
+      </c>
+      <c r="F325" t="s">
+        <v>334</v>
+      </c>
+      <c r="G325" t="s">
+        <v>289</v>
+      </c>
+      <c r="I325" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>10</v>
+      </c>
+      <c r="B326" t="s">
+        <v>287</v>
+      </c>
+      <c r="C326" t="s">
+        <v>290</v>
+      </c>
+      <c r="E326" t="s">
+        <v>335</v>
+      </c>
+      <c r="F326" t="s">
+        <v>336</v>
+      </c>
+      <c r="G326" t="s">
+        <v>289</v>
+      </c>
+      <c r="I326" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>10</v>
+      </c>
+      <c r="B327" t="s">
+        <v>287</v>
+      </c>
+      <c r="C327" t="s">
+        <v>290</v>
+      </c>
+      <c r="E327" t="s">
+        <v>337</v>
+      </c>
+      <c r="F327" t="s">
+        <v>338</v>
+      </c>
+      <c r="G327" t="s">
+        <v>289</v>
+      </c>
+      <c r="I327" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>10</v>
+      </c>
+      <c r="B328" t="s">
+        <v>287</v>
+      </c>
+      <c r="C328" t="s">
+        <v>339</v>
+      </c>
+      <c r="E328" t="s">
+        <v>340</v>
+      </c>
+      <c r="F328" t="s">
+        <v>341</v>
+      </c>
+      <c r="G328" t="s">
+        <v>289</v>
+      </c>
+      <c r="I328" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J185" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J328" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6017,27 +10015,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>239</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>241</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
